--- a/Datos ESPARTACO/Parámetros para análisis de Antares/resultados perfiles halpha 2024, 2025 y 2026.xlsx
+++ b/Datos ESPARTACO/Parámetros para análisis de Antares/resultados perfiles halpha 2024, 2025 y 2026.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H67"/>
+  <dimension ref="A1:H58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1553,7 +1553,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Septiembre 06-2025</t>
+          <t>Julio 24-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1562,28 +1562,28 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>6562.463</v>
+        <v>6562.019</v>
       </c>
       <c r="D38" t="n">
-        <v>-5.3e-05</v>
+        <v>-0.000121</v>
       </c>
       <c r="E38" t="n">
-        <v>-15.9468</v>
+        <v>-36.2429</v>
       </c>
       <c r="F38" t="n">
-        <v>0.3083</v>
+        <v>0.269</v>
       </c>
       <c r="G38" t="n">
-        <v>1.583</v>
+        <v>1.081</v>
       </c>
       <c r="H38" t="n">
-        <v>0.8633</v>
+        <v>0.4337</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Septiembre 06-2025</t>
+          <t>Julio 24-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1592,28 +1592,28 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>6563.167</v>
+        <v>6562.853</v>
       </c>
       <c r="D39" t="n">
-        <v>5.4e-05</v>
+        <v>6e-06</v>
       </c>
       <c r="E39" t="n">
-        <v>16.2206</v>
+        <v>1.8737</v>
       </c>
       <c r="F39" t="n">
-        <v>0.7306</v>
+        <v>0.6818</v>
       </c>
       <c r="G39" t="n">
-        <v>1.115</v>
+        <v>1.214</v>
       </c>
       <c r="H39" t="n">
-        <v>1.0315</v>
+        <v>1.0234</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Septiembre 06-2025</t>
+          <t>Julio 24-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1622,28 +1622,28 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>6564.038</v>
+        <v>6563.793</v>
       </c>
       <c r="D40" t="n">
-        <v>9.8e-05</v>
+        <v>6e-05</v>
       </c>
       <c r="E40" t="n">
-        <v>29.3</v>
+        <v>18.07</v>
       </c>
       <c r="F40" t="n">
-        <v>0.4769</v>
+        <v>0.4884</v>
       </c>
       <c r="G40" t="n">
-        <v>0.986</v>
+        <v>1.025</v>
       </c>
       <c r="H40" t="n">
-        <v>0.6297</v>
+        <v>0.6531</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Julio 22-2026</t>
+          <t>Julio 27-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1652,28 +1652,28 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>6562.406</v>
+        <v>6561.891</v>
       </c>
       <c r="D41" t="n">
-        <v>-6.2e-05</v>
+        <v>-0.00014</v>
       </c>
       <c r="E41" t="n">
-        <v>-18.5634</v>
+        <v>-42.063</v>
       </c>
       <c r="F41" t="n">
-        <v>0.3182</v>
+        <v>0.2086</v>
       </c>
       <c r="G41" t="n">
-        <v>1.476</v>
+        <v>0.959</v>
       </c>
       <c r="H41" t="n">
-        <v>0.8136</v>
+        <v>0.2413</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Julio 22-2026</t>
+          <t>Julio 27-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1682,28 +1682,28 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>6562.988</v>
+        <v>6562.889</v>
       </c>
       <c r="D42" t="n">
-        <v>2.7e-05</v>
+        <v>1.2e-05</v>
       </c>
       <c r="E42" t="n">
-        <v>8.037800000000001</v>
+        <v>3.5257</v>
       </c>
       <c r="F42" t="n">
-        <v>0.7635</v>
+        <v>0.6597</v>
       </c>
       <c r="G42" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="H42" t="n">
-        <v>1.0606</v>
+        <v>0.9416</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Julio 22-2026</t>
+          <t>Julio 27-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1712,28 +1712,28 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>6563.88</v>
+        <v>6563.795</v>
       </c>
       <c r="D43" t="n">
-        <v>7.4e-05</v>
+        <v>6.1e-05</v>
       </c>
       <c r="E43" t="n">
-        <v>22.069</v>
+        <v>18.19</v>
       </c>
       <c r="F43" t="n">
-        <v>0.4564</v>
+        <v>0.5004</v>
       </c>
       <c r="G43" t="n">
-        <v>0.925</v>
+        <v>1.027</v>
       </c>
       <c r="H43" t="n">
-        <v>0.587</v>
+        <v>0.6543</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Julio 24-2026</t>
+          <t>Agosto 06-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1742,28 +1742,28 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>6562.019</v>
+        <v>6562.148</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.000121</v>
+        <v>-0.000101</v>
       </c>
       <c r="E44" t="n">
-        <v>-36.2429</v>
+        <v>-30.3483</v>
       </c>
       <c r="F44" t="n">
-        <v>0.269</v>
+        <v>0.3547</v>
       </c>
       <c r="G44" t="n">
-        <v>1.081</v>
+        <v>1.051</v>
       </c>
       <c r="H44" t="n">
-        <v>0.4337</v>
+        <v>0.4543</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Julio 24-2026</t>
+          <t>Agosto 06-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1772,28 +1772,28 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>6562.853</v>
+        <v>6562.842</v>
       </c>
       <c r="D45" t="n">
-        <v>6e-06</v>
+        <v>5e-06</v>
       </c>
       <c r="E45" t="n">
-        <v>1.8737</v>
+        <v>1.3536</v>
       </c>
       <c r="F45" t="n">
-        <v>0.6818</v>
+        <v>0.716</v>
       </c>
       <c r="G45" t="n">
-        <v>1.214</v>
+        <v>1.293</v>
       </c>
       <c r="H45" t="n">
-        <v>1.0234</v>
+        <v>1.128</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Julio 24-2026</t>
+          <t>Agosto 06-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1802,28 +1802,28 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>6563.793</v>
+        <v>6563.849</v>
       </c>
       <c r="D46" t="n">
-        <v>6e-05</v>
+        <v>6.9e-05</v>
       </c>
       <c r="E46" t="n">
-        <v>18.07</v>
+        <v>20.64</v>
       </c>
       <c r="F46" t="n">
-        <v>0.4884</v>
+        <v>0.4954</v>
       </c>
       <c r="G46" t="n">
         <v>1.025</v>
       </c>
       <c r="H46" t="n">
-        <v>0.6531</v>
+        <v>0.6525</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Julio 27-2026</t>
+          <t>Agosto 10-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1832,28 +1832,28 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>6561.891</v>
+        <v>6562.177</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.00014</v>
+        <v>-9.7e-05</v>
       </c>
       <c r="E47" t="n">
-        <v>-42.063</v>
+        <v>-29.0068</v>
       </c>
       <c r="F47" t="n">
-        <v>0.2086</v>
+        <v>0.3875</v>
       </c>
       <c r="G47" t="n">
-        <v>0.959</v>
+        <v>1.134</v>
       </c>
       <c r="H47" t="n">
-        <v>0.2413</v>
+        <v>0.6049</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Julio 27-2026</t>
+          <t>Agosto 10-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1862,28 +1862,28 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>6562.889</v>
+        <v>6562.873</v>
       </c>
       <c r="D48" t="n">
-        <v>1.2e-05</v>
+        <v>9e-06</v>
       </c>
       <c r="E48" t="n">
-        <v>3.5257</v>
+        <v>2.7949</v>
       </c>
       <c r="F48" t="n">
-        <v>0.6597</v>
+        <v>0.7371</v>
       </c>
       <c r="G48" t="n">
-        <v>1.13</v>
+        <v>1.307</v>
       </c>
       <c r="H48" t="n">
-        <v>0.9416</v>
+        <v>1.1687</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Julio 27-2026</t>
+          <t>Agosto 10-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1892,28 +1892,28 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>6563.795</v>
+        <v>6563.874</v>
       </c>
       <c r="D49" t="n">
-        <v>6.1e-05</v>
+        <v>7.3e-05</v>
       </c>
       <c r="E49" t="n">
-        <v>18.19</v>
+        <v>21.77</v>
       </c>
       <c r="F49" t="n">
-        <v>0.5004</v>
+        <v>0.4977</v>
       </c>
       <c r="G49" t="n">
-        <v>1.027</v>
+        <v>1.041</v>
       </c>
       <c r="H49" t="n">
-        <v>0.6543</v>
+        <v>0.6685</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Agosto 06-2026</t>
+          <t>Agosto 13-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>6562.148</v>
+        <v>6562.166</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.000101</v>
+        <v>-9.8e-05</v>
       </c>
       <c r="E50" t="n">
-        <v>-30.3483</v>
+        <v>-29.5136</v>
       </c>
       <c r="F50" t="n">
-        <v>0.3547</v>
+        <v>0.3471</v>
       </c>
       <c r="G50" t="n">
-        <v>1.051</v>
+        <v>1.111</v>
       </c>
       <c r="H50" t="n">
-        <v>0.4543</v>
+        <v>0.5417</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Agosto 06-2026</t>
+          <t>Agosto 13-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1952,28 +1952,28 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>6562.842</v>
+        <v>6562.875</v>
       </c>
       <c r="D51" t="n">
-        <v>5e-06</v>
+        <v>1e-05</v>
       </c>
       <c r="E51" t="n">
-        <v>1.3536</v>
+        <v>2.8908</v>
       </c>
       <c r="F51" t="n">
-        <v>0.716</v>
+        <v>0.7149</v>
       </c>
       <c r="G51" t="n">
-        <v>1.293</v>
+        <v>1.311</v>
       </c>
       <c r="H51" t="n">
-        <v>1.128</v>
+        <v>1.1508</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Agosto 06-2026</t>
+          <t>Agosto 13-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1982,28 +1982,28 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>6563.849</v>
+        <v>6563.87</v>
       </c>
       <c r="D52" t="n">
-        <v>6.9e-05</v>
+        <v>7.2e-05</v>
       </c>
       <c r="E52" t="n">
-        <v>20.64</v>
+        <v>21.59</v>
       </c>
       <c r="F52" t="n">
-        <v>0.4954</v>
+        <v>0.4917</v>
       </c>
       <c r="G52" t="n">
-        <v>1.025</v>
+        <v>1.052</v>
       </c>
       <c r="H52" t="n">
-        <v>0.6525</v>
+        <v>0.6801</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Agosto 10-2026</t>
+          <t>Agosto 28-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2012,28 +2012,28 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>6562.177</v>
+        <v>6562.141</v>
       </c>
       <c r="D53" t="n">
-        <v>-9.7e-05</v>
+        <v>-0.000102</v>
       </c>
       <c r="E53" t="n">
-        <v>-29.0068</v>
+        <v>-30.6728</v>
       </c>
       <c r="F53" t="n">
-        <v>0.3875</v>
+        <v>0.3028</v>
       </c>
       <c r="G53" t="n">
-        <v>1.134</v>
+        <v>1.096</v>
       </c>
       <c r="H53" t="n">
-        <v>0.6049</v>
+        <v>0.469</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Agosto 10-2026</t>
+          <t>Agosto 28-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2042,28 +2042,28 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>6562.873</v>
+        <v>6562.98</v>
       </c>
       <c r="D54" t="n">
-        <v>9e-06</v>
+        <v>2.6e-05</v>
       </c>
       <c r="E54" t="n">
-        <v>2.7949</v>
+        <v>7.66</v>
       </c>
       <c r="F54" t="n">
-        <v>0.7371</v>
+        <v>0.7614</v>
       </c>
       <c r="G54" t="n">
-        <v>1.307</v>
+        <v>1.282</v>
       </c>
       <c r="H54" t="n">
-        <v>1.1687</v>
+        <v>1.077</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Agosto 10-2026</t>
+          <t>Agosto 28-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2072,28 +2072,28 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>6563.874</v>
+        <v>6563.948</v>
       </c>
       <c r="D55" t="n">
-        <v>7.3e-05</v>
+        <v>8.4e-05</v>
       </c>
       <c r="E55" t="n">
-        <v>21.77</v>
+        <v>25.15</v>
       </c>
       <c r="F55" t="n">
-        <v>0.4977</v>
+        <v>0.5489000000000001</v>
       </c>
       <c r="G55" t="n">
-        <v>1.041</v>
+        <v>1.07</v>
       </c>
       <c r="H55" t="n">
-        <v>0.6685</v>
+        <v>0.6982</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Agosto 13-2026</t>
+          <t>Septiembre 07-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2102,28 +2102,28 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>6562.166</v>
+        <v>6562.106</v>
       </c>
       <c r="D56" t="n">
-        <v>-9.8e-05</v>
+        <v>-0.000108</v>
       </c>
       <c r="E56" t="n">
-        <v>-29.5136</v>
+        <v>-32.2395</v>
       </c>
       <c r="F56" t="n">
-        <v>0.3471</v>
+        <v>0.2979</v>
       </c>
       <c r="G56" t="n">
-        <v>1.111</v>
+        <v>1.046</v>
       </c>
       <c r="H56" t="n">
-        <v>0.5417</v>
+        <v>0.4257</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Agosto 13-2026</t>
+          <t>Septiembre 07-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2132,28 +2132,28 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>6562.875</v>
+        <v>6562.949</v>
       </c>
       <c r="D57" t="n">
-        <v>1e-05</v>
+        <v>2.1e-05</v>
       </c>
       <c r="E57" t="n">
-        <v>2.8908</v>
+        <v>6.2449</v>
       </c>
       <c r="F57" t="n">
-        <v>0.7149</v>
+        <v>0.7348</v>
       </c>
       <c r="G57" t="n">
-        <v>1.311</v>
+        <v>1.307</v>
       </c>
       <c r="H57" t="n">
-        <v>1.1508</v>
+        <v>1.0736</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Agosto 13-2026</t>
+          <t>Septiembre 07-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2162,291 +2162,21 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>6563.87</v>
+        <v>6563.924</v>
       </c>
       <c r="D58" t="n">
-        <v>7.2e-05</v>
+        <v>8.000000000000001e-05</v>
       </c>
       <c r="E58" t="n">
-        <v>21.59</v>
+        <v>24.07</v>
       </c>
       <c r="F58" t="n">
-        <v>0.4917</v>
+        <v>0.5484</v>
       </c>
       <c r="G58" t="n">
-        <v>1.052</v>
+        <v>1.126</v>
       </c>
       <c r="H58" t="n">
-        <v>0.6801</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Agosto 26-2026</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Emisión Azul Hα</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
-        <v>6562.486</v>
-      </c>
-      <c r="D59" t="n">
-        <v>-5e-05</v>
-      </c>
-      <c r="E59" t="n">
-        <v>-14.8782</v>
-      </c>
-      <c r="F59" t="n">
-        <v>0.4537</v>
-      </c>
-      <c r="G59" t="n">
-        <v>1.241</v>
-      </c>
-      <c r="H59" t="n">
-        <v>0.9314</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Agosto 26-2026</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Absorción Hα</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
-        <v>6563.11</v>
-      </c>
-      <c r="D60" t="n">
-        <v>4.5e-05</v>
-      </c>
-      <c r="E60" t="n">
-        <v>13.6078</v>
-      </c>
-      <c r="F60" t="n">
-        <v>0.8577</v>
-      </c>
-      <c r="G60" t="n">
-        <v>1.156</v>
-      </c>
-      <c r="H60" t="n">
-        <v>1.1613</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Agosto 26-2026</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Absorción Cobalto</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
-        <v>6564.025</v>
-      </c>
-      <c r="D61" t="n">
-        <v>9.6e-05</v>
-      </c>
-      <c r="E61" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="F61" t="n">
-        <v>0.5155</v>
-      </c>
-      <c r="G61" t="n">
-        <v>0.949</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0.6075</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Agosto 28-2026</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Emisión Azul Hα</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
-        <v>6562.141</v>
-      </c>
-      <c r="D62" t="n">
-        <v>-0.000102</v>
-      </c>
-      <c r="E62" t="n">
-        <v>-30.6728</v>
-      </c>
-      <c r="F62" t="n">
-        <v>0.3028</v>
-      </c>
-      <c r="G62" t="n">
-        <v>1.096</v>
-      </c>
-      <c r="H62" t="n">
-        <v>0.469</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Agosto 28-2026</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Absorción Hα</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>6562.98</v>
-      </c>
-      <c r="D63" t="n">
-        <v>2.6e-05</v>
-      </c>
-      <c r="E63" t="n">
-        <v>7.66</v>
-      </c>
-      <c r="F63" t="n">
-        <v>0.7614</v>
-      </c>
-      <c r="G63" t="n">
-        <v>1.282</v>
-      </c>
-      <c r="H63" t="n">
-        <v>1.077</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Agosto 28-2026</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Absorción Cobalto</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
-        <v>6563.948</v>
-      </c>
-      <c r="D64" t="n">
-        <v>8.4e-05</v>
-      </c>
-      <c r="E64" t="n">
-        <v>25.15</v>
-      </c>
-      <c r="F64" t="n">
-        <v>0.5489000000000001</v>
-      </c>
-      <c r="G64" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="H64" t="n">
-        <v>0.6982</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Septiembre 07-2026</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Emisión Azul Hα</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
-        <v>6562.106</v>
-      </c>
-      <c r="D65" t="n">
-        <v>-0.000108</v>
-      </c>
-      <c r="E65" t="n">
-        <v>-32.2395</v>
-      </c>
-      <c r="F65" t="n">
-        <v>0.2979</v>
-      </c>
-      <c r="G65" t="n">
-        <v>1.046</v>
-      </c>
-      <c r="H65" t="n">
-        <v>0.4257</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Septiembre 07-2026</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Absorción Hα</t>
-        </is>
-      </c>
-      <c r="C66" t="n">
-        <v>6562.949</v>
-      </c>
-      <c r="D66" t="n">
-        <v>2.1e-05</v>
-      </c>
-      <c r="E66" t="n">
-        <v>6.2449</v>
-      </c>
-      <c r="F66" t="n">
-        <v>0.7348</v>
-      </c>
-      <c r="G66" t="n">
-        <v>1.307</v>
-      </c>
-      <c r="H66" t="n">
-        <v>1.0736</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Septiembre 07-2026</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Absorción Cobalto</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>6563.924</v>
-      </c>
-      <c r="D67" t="n">
-        <v>8.000000000000001e-05</v>
-      </c>
-      <c r="E67" t="n">
-        <v>24.07</v>
-      </c>
-      <c r="F67" t="n">
-        <v>0.5484</v>
-      </c>
-      <c r="G67" t="n">
-        <v>1.126</v>
-      </c>
-      <c r="H67" t="n">
         <v>0.7531</v>
       </c>
     </row>

--- a/Datos ESPARTACO/Parámetros para análisis de Antares/resultados perfiles halpha 2024, 2025 y 2026.xlsx
+++ b/Datos ESPARTACO/Parámetros para análisis de Antares/resultados perfiles halpha 2024, 2025 y 2026.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H58"/>
+  <dimension ref="A1:I67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,20 +451,25 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Velocidad [km/s]</t>
+          <t>Velocidad obs. [km/s]</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Velocidad heliocéntrica [km/s]</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Profundidad / Altura</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>FWHM [Å]</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>EW [Å]</t>
         </is>
@@ -488,15 +493,18 @@
         <v>-5.5e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>-16.6369</v>
+        <v>-16.64</v>
       </c>
       <c r="F2" t="n">
+        <v>-35.29</v>
+      </c>
+      <c r="G2" t="n">
         <v>0.3898</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>1.555</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>0.9323</v>
       </c>
     </row>
@@ -518,15 +526,18 @@
         <v>1.4e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>4.2427</v>
+        <v>4.24</v>
       </c>
       <c r="F3" t="n">
+        <v>-14.41</v>
+      </c>
+      <c r="G3" t="n">
         <v>0.9122</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>1.059</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>1.1795</v>
       </c>
     </row>
@@ -548,15 +559,18 @@
         <v>6.4e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>19.0999</v>
+        <v>19.1</v>
       </c>
       <c r="F4" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="G4" t="n">
         <v>0.4944</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>0.927</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>0.5872000000000001</v>
       </c>
     </row>
@@ -578,15 +592,18 @@
         <v>-0.000124</v>
       </c>
       <c r="E5" t="n">
-        <v>-37.2771</v>
+        <v>-37.28</v>
       </c>
       <c r="F5" t="n">
+        <v>-59.8</v>
+      </c>
+      <c r="G5" t="n">
         <v>0.1879</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>0.982</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>0.2444</v>
       </c>
     </row>
@@ -608,15 +625,18 @@
         <v>3.4e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>10.3394</v>
+        <v>10.34</v>
       </c>
       <c r="F6" t="n">
+        <v>-12.18</v>
+      </c>
+      <c r="G6" t="n">
         <v>0.6215000000000001</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>0.875</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>0.6232</v>
       </c>
     </row>
@@ -641,12 +661,15 @@
         <v>21.86</v>
       </c>
       <c r="F7" t="n">
+        <v>-0.66</v>
+      </c>
+      <c r="G7" t="n">
         <v>0.5265</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>0.883</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>0.5611</v>
       </c>
     </row>
@@ -668,15 +691,18 @@
         <v>-4.1e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>-12.3499</v>
+        <v>-12.35</v>
       </c>
       <c r="F8" t="n">
+        <v>-40.69</v>
+      </c>
+      <c r="G8" t="n">
         <v>0.5289</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>1.223</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>0.9347</v>
       </c>
     </row>
@@ -698,15 +724,18 @@
         <v>3.2e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>9.7233</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="F9" t="n">
+        <v>-18.62</v>
+      </c>
+      <c r="G9" t="n">
         <v>0.9089</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>1.164</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>1.309</v>
       </c>
     </row>
@@ -731,12 +760,15 @@
         <v>27.47</v>
       </c>
       <c r="F10" t="n">
+        <v>-0.87</v>
+      </c>
+      <c r="G10" t="n">
         <v>0.4879</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>0.926</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>0.5868</v>
       </c>
     </row>
@@ -758,15 +790,18 @@
         <v>-4.8e-05</v>
       </c>
       <c r="E11" t="n">
-        <v>-14.3455</v>
+        <v>-14.35</v>
       </c>
       <c r="F11" t="n">
+        <v>-43.7</v>
+      </c>
+      <c r="G11" t="n">
         <v>0.5451</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>1.117</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>0.8788</v>
       </c>
     </row>
@@ -788,15 +823,18 @@
         <v>3.5e-05</v>
       </c>
       <c r="E12" t="n">
-        <v>10.6416</v>
+        <v>10.64</v>
       </c>
       <c r="F12" t="n">
+        <v>-18.71</v>
+      </c>
+      <c r="G12" t="n">
         <v>0.9061</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>1.208</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>1.2492</v>
       </c>
     </row>
@@ -821,12 +859,15 @@
         <v>28.69</v>
       </c>
       <c r="F13" t="n">
+        <v>-0.66</v>
+      </c>
+      <c r="G13" t="n">
         <v>0.5288</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>0.968</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>0.6183</v>
       </c>
     </row>
@@ -848,15 +889,18 @@
         <v>-4.8e-05</v>
       </c>
       <c r="E14" t="n">
-        <v>-14.4749</v>
+        <v>-14.47</v>
       </c>
       <c r="F14" t="n">
+        <v>-44.04</v>
+      </c>
+      <c r="G14" t="n">
         <v>0.3796</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>1.317</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>0.8424</v>
       </c>
     </row>
@@ -878,15 +922,18 @@
         <v>4.5e-05</v>
       </c>
       <c r="E15" t="n">
-        <v>13.357</v>
+        <v>13.36</v>
       </c>
       <c r="F15" t="n">
+        <v>-16.21</v>
+      </c>
+      <c r="G15" t="n">
         <v>0.7659</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>1.175</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>1.1158</v>
       </c>
     </row>
@@ -911,12 +958,15 @@
         <v>28.76</v>
       </c>
       <c r="F16" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="G16" t="n">
         <v>0.4869</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>1.008</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>0.6425999999999999</v>
       </c>
     </row>
@@ -938,15 +988,18 @@
         <v>-6.8e-05</v>
       </c>
       <c r="E17" t="n">
-        <v>-20.4338</v>
+        <v>-20.43</v>
       </c>
       <c r="F17" t="n">
+        <v>-48.81</v>
+      </c>
+      <c r="G17" t="n">
         <v>0.2681</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>1.281</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>0.4125</v>
       </c>
     </row>
@@ -968,15 +1021,18 @@
         <v>4.4e-05</v>
       </c>
       <c r="E18" t="n">
-        <v>13.2045</v>
+        <v>13.2</v>
       </c>
       <c r="F18" t="n">
+        <v>-15.18</v>
+      </c>
+      <c r="G18" t="n">
         <v>0.6959</v>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>1.095</v>
       </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
         <v>0.915</v>
       </c>
     </row>
@@ -1001,12 +1057,15 @@
         <v>27.73</v>
       </c>
       <c r="F19" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="G19" t="n">
         <v>0.5024999999999999</v>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>1.002</v>
       </c>
-      <c r="H19" t="n">
+      <c r="I19" t="n">
         <v>0.639</v>
       </c>
     </row>
@@ -1028,15 +1087,18 @@
         <v>-5.6e-05</v>
       </c>
       <c r="E20" t="n">
-        <v>-16.8025</v>
+        <v>-16.8</v>
       </c>
       <c r="F20" t="n">
+        <v>-44.29</v>
+      </c>
+      <c r="G20" t="n">
         <v>0.4913</v>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>1.14</v>
       </c>
-      <c r="H20" t="n">
+      <c r="I20" t="n">
         <v>0.7803</v>
       </c>
     </row>
@@ -1058,15 +1120,18 @@
         <v>2.8e-05</v>
       </c>
       <c r="E21" t="n">
-        <v>8.5372</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="F21" t="n">
+        <v>-18.95</v>
+      </c>
+      <c r="G21" t="n">
         <v>0.7731</v>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>1.268</v>
       </c>
-      <c r="H21" t="n">
+      <c r="I21" t="n">
         <v>1.1841</v>
       </c>
     </row>
@@ -1091,12 +1156,15 @@
         <v>27.14</v>
       </c>
       <c r="F22" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="G22" t="n">
         <v>0.4998</v>
       </c>
-      <c r="G22" t="n">
+      <c r="H22" t="n">
         <v>1.041</v>
       </c>
-      <c r="H22" t="n">
+      <c r="I22" t="n">
         <v>0.6685</v>
       </c>
     </row>
@@ -1118,15 +1186,18 @@
         <v>-6.499999999999999e-05</v>
       </c>
       <c r="E23" t="n">
-        <v>-19.3429</v>
+        <v>-19.34</v>
       </c>
       <c r="F23" t="n">
+        <v>-45.36</v>
+      </c>
+      <c r="G23" t="n">
         <v>0.4258</v>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>1.119</v>
       </c>
-      <c r="H23" t="n">
+      <c r="I23" t="n">
         <v>0.5682</v>
       </c>
     </row>
@@ -1148,15 +1219,18 @@
         <v>3e-05</v>
       </c>
       <c r="E24" t="n">
-        <v>8.9337</v>
+        <v>8.93</v>
       </c>
       <c r="F24" t="n">
+        <v>-17.09</v>
+      </c>
+      <c r="G24" t="n">
         <v>0.7266</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>1.234</v>
       </c>
-      <c r="H24" t="n">
+      <c r="I24" t="n">
         <v>1.069</v>
       </c>
     </row>
@@ -1181,12 +1255,15 @@
         <v>26.71</v>
       </c>
       <c r="F25" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="G25" t="n">
         <v>0.5061</v>
       </c>
-      <c r="G25" t="n">
+      <c r="H25" t="n">
         <v>1.025</v>
       </c>
-      <c r="H25" t="n">
+      <c r="I25" t="n">
         <v>0.6525</v>
       </c>
     </row>
@@ -1208,15 +1285,18 @@
         <v>-7.8e-05</v>
       </c>
       <c r="E26" t="n">
-        <v>-23.4498</v>
+        <v>-23.45</v>
       </c>
       <c r="F26" t="n">
+        <v>-46.56</v>
+      </c>
+      <c r="G26" t="n">
         <v>0.4244</v>
       </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
         <v>1.264</v>
       </c>
-      <c r="H26" t="n">
+      <c r="I26" t="n">
         <v>0.7702</v>
       </c>
     </row>
@@ -1238,15 +1318,18 @@
         <v>2.6e-05</v>
       </c>
       <c r="E27" t="n">
-        <v>7.9443</v>
+        <v>7.94</v>
       </c>
       <c r="F27" t="n">
+        <v>-15.17</v>
+      </c>
+      <c r="G27" t="n">
         <v>0.825</v>
       </c>
-      <c r="G27" t="n">
+      <c r="H27" t="n">
         <v>1.177</v>
       </c>
-      <c r="H27" t="n">
+      <c r="I27" t="n">
         <v>1.2804</v>
       </c>
     </row>
@@ -1271,12 +1354,15 @@
         <v>22.64</v>
       </c>
       <c r="F28" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="G28" t="n">
         <v>0.5544</v>
       </c>
-      <c r="G28" t="n">
+      <c r="H28" t="n">
         <v>1.053</v>
       </c>
-      <c r="H28" t="n">
+      <c r="I28" t="n">
         <v>0.6811</v>
       </c>
     </row>
@@ -1298,15 +1384,18 @@
         <v>-9.1e-05</v>
       </c>
       <c r="E29" t="n">
-        <v>-27.4297</v>
+        <v>-27.43</v>
       </c>
       <c r="F29" t="n">
+        <v>-48.48</v>
+      </c>
+      <c r="G29" t="n">
         <v>0.3821</v>
       </c>
-      <c r="G29" t="n">
+      <c r="H29" t="n">
         <v>1.244</v>
       </c>
-      <c r="H29" t="n">
+      <c r="I29" t="n">
         <v>0.6911</v>
       </c>
     </row>
@@ -1328,15 +1417,18 @@
         <v>1.9e-05</v>
       </c>
       <c r="E30" t="n">
-        <v>5.8222</v>
+        <v>5.82</v>
       </c>
       <c r="F30" t="n">
+        <v>-15.23</v>
+      </c>
+      <c r="G30" t="n">
         <v>0.7957</v>
       </c>
-      <c r="G30" t="n">
+      <c r="H30" t="n">
         <v>1.154</v>
       </c>
-      <c r="H30" t="n">
+      <c r="I30" t="n">
         <v>1.1765</v>
       </c>
     </row>
@@ -1361,12 +1453,15 @@
         <v>20.25</v>
       </c>
       <c r="F31" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="G31" t="n">
         <v>0.5538</v>
       </c>
-      <c r="G31" t="n">
+      <c r="H31" t="n">
         <v>1.043</v>
       </c>
-      <c r="H31" t="n">
+      <c r="I31" t="n">
         <v>0.6707</v>
       </c>
     </row>
@@ -1388,15 +1483,18 @@
         <v>-9.2e-05</v>
       </c>
       <c r="E32" t="n">
-        <v>-27.5046</v>
+        <v>-27.5</v>
       </c>
       <c r="F32" t="n">
+        <v>-48.22</v>
+      </c>
+      <c r="G32" t="n">
         <v>0.3988</v>
       </c>
-      <c r="G32" t="n">
+      <c r="H32" t="n">
         <v>1.093</v>
       </c>
-      <c r="H32" t="n">
+      <c r="I32" t="n">
         <v>0.5226</v>
       </c>
     </row>
@@ -1418,15 +1516,18 @@
         <v>9e-06</v>
       </c>
       <c r="E33" t="n">
-        <v>2.7643</v>
+        <v>2.76</v>
       </c>
       <c r="F33" t="n">
+        <v>-17.96</v>
+      </c>
+      <c r="G33" t="n">
         <v>0.6762</v>
       </c>
-      <c r="G33" t="n">
+      <c r="H33" t="n">
         <v>1.252</v>
       </c>
-      <c r="H33" t="n">
+      <c r="I33" t="n">
         <v>1.0153</v>
       </c>
     </row>
@@ -1451,12 +1552,15 @@
         <v>19.8</v>
       </c>
       <c r="F34" t="n">
+        <v>-0.92</v>
+      </c>
+      <c r="G34" t="n">
         <v>0.5034999999999999</v>
       </c>
-      <c r="G34" t="n">
+      <c r="H34" t="n">
         <v>1.025</v>
       </c>
-      <c r="H34" t="n">
+      <c r="I34" t="n">
         <v>0.6525</v>
       </c>
     </row>
@@ -1478,15 +1582,18 @@
         <v>-0.000107</v>
       </c>
       <c r="E35" t="n">
-        <v>-32.0071</v>
+        <v>-32.01</v>
       </c>
       <c r="F35" t="n">
+        <v>-50.44</v>
+      </c>
+      <c r="G35" t="n">
         <v>0.3881</v>
       </c>
-      <c r="G35" t="n">
+      <c r="H35" t="n">
         <v>1.063</v>
       </c>
-      <c r="H35" t="n">
+      <c r="I35" t="n">
         <v>0.4802</v>
       </c>
     </row>
@@ -1508,15 +1615,18 @@
         <v>1e-05</v>
       </c>
       <c r="E36" t="n">
-        <v>3.0169</v>
+        <v>3.02</v>
       </c>
       <c r="F36" t="n">
+        <v>-15.41</v>
+      </c>
+      <c r="G36" t="n">
         <v>0.641</v>
       </c>
-      <c r="G36" t="n">
+      <c r="H36" t="n">
         <v>1.231</v>
       </c>
-      <c r="H36" t="n">
+      <c r="I36" t="n">
         <v>1.0231</v>
       </c>
     </row>
@@ -1541,12 +1651,15 @@
         <v>17.87</v>
       </c>
       <c r="F37" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="G37" t="n">
         <v>0.5184</v>
       </c>
-      <c r="G37" t="n">
+      <c r="H37" t="n">
         <v>1.04</v>
       </c>
-      <c r="H37" t="n">
+      <c r="I37" t="n">
         <v>0.6683</v>
       </c>
     </row>
@@ -1568,15 +1681,18 @@
         <v>-0.000121</v>
       </c>
       <c r="E38" t="n">
-        <v>-36.2429</v>
+        <v>-36.24</v>
       </c>
       <c r="F38" t="n">
+        <v>-59.37</v>
+      </c>
+      <c r="G38" t="n">
         <v>0.269</v>
       </c>
-      <c r="G38" t="n">
+      <c r="H38" t="n">
         <v>1.081</v>
       </c>
-      <c r="H38" t="n">
+      <c r="I38" t="n">
         <v>0.4337</v>
       </c>
     </row>
@@ -1598,15 +1714,18 @@
         <v>6e-06</v>
       </c>
       <c r="E39" t="n">
-        <v>1.8737</v>
+        <v>1.87</v>
       </c>
       <c r="F39" t="n">
+        <v>-21.26</v>
+      </c>
+      <c r="G39" t="n">
         <v>0.6818</v>
       </c>
-      <c r="G39" t="n">
+      <c r="H39" t="n">
         <v>1.214</v>
       </c>
-      <c r="H39" t="n">
+      <c r="I39" t="n">
         <v>1.0234</v>
       </c>
     </row>
@@ -1631,12 +1750,15 @@
         <v>18.07</v>
       </c>
       <c r="F40" t="n">
+        <v>-5.06</v>
+      </c>
+      <c r="G40" t="n">
         <v>0.4884</v>
       </c>
-      <c r="G40" t="n">
+      <c r="H40" t="n">
         <v>1.025</v>
       </c>
-      <c r="H40" t="n">
+      <c r="I40" t="n">
         <v>0.6531</v>
       </c>
     </row>
@@ -1658,15 +1780,18 @@
         <v>-0.00014</v>
       </c>
       <c r="E41" t="n">
-        <v>-42.063</v>
+        <v>-42.06</v>
       </c>
       <c r="F41" t="n">
+        <v>-65.98999999999999</v>
+      </c>
+      <c r="G41" t="n">
         <v>0.2086</v>
       </c>
-      <c r="G41" t="n">
+      <c r="H41" t="n">
         <v>0.959</v>
       </c>
-      <c r="H41" t="n">
+      <c r="I41" t="n">
         <v>0.2413</v>
       </c>
     </row>
@@ -1688,15 +1813,18 @@
         <v>1.2e-05</v>
       </c>
       <c r="E42" t="n">
-        <v>3.5257</v>
+        <v>3.53</v>
       </c>
       <c r="F42" t="n">
+        <v>-20.4</v>
+      </c>
+      <c r="G42" t="n">
         <v>0.6597</v>
       </c>
-      <c r="G42" t="n">
+      <c r="H42" t="n">
         <v>1.13</v>
       </c>
-      <c r="H42" t="n">
+      <c r="I42" t="n">
         <v>0.9416</v>
       </c>
     </row>
@@ -1721,12 +1849,15 @@
         <v>18.19</v>
       </c>
       <c r="F43" t="n">
+        <v>-5.74</v>
+      </c>
+      <c r="G43" t="n">
         <v>0.5004</v>
       </c>
-      <c r="G43" t="n">
+      <c r="H43" t="n">
         <v>1.027</v>
       </c>
-      <c r="H43" t="n">
+      <c r="I43" t="n">
         <v>0.6543</v>
       </c>
     </row>
@@ -1748,15 +1879,18 @@
         <v>-0.000101</v>
       </c>
       <c r="E44" t="n">
-        <v>-30.3483</v>
+        <v>-30.35</v>
       </c>
       <c r="F44" t="n">
+        <v>-56.85</v>
+      </c>
+      <c r="G44" t="n">
         <v>0.3547</v>
       </c>
-      <c r="G44" t="n">
+      <c r="H44" t="n">
         <v>1.051</v>
       </c>
-      <c r="H44" t="n">
+      <c r="I44" t="n">
         <v>0.4543</v>
       </c>
     </row>
@@ -1778,15 +1912,18 @@
         <v>5e-06</v>
       </c>
       <c r="E45" t="n">
-        <v>1.3536</v>
+        <v>1.35</v>
       </c>
       <c r="F45" t="n">
+        <v>-25.15</v>
+      </c>
+      <c r="G45" t="n">
         <v>0.716</v>
       </c>
-      <c r="G45" t="n">
+      <c r="H45" t="n">
         <v>1.293</v>
       </c>
-      <c r="H45" t="n">
+      <c r="I45" t="n">
         <v>1.128</v>
       </c>
     </row>
@@ -1811,12 +1948,15 @@
         <v>20.64</v>
       </c>
       <c r="F46" t="n">
+        <v>-5.86</v>
+      </c>
+      <c r="G46" t="n">
         <v>0.4954</v>
       </c>
-      <c r="G46" t="n">
+      <c r="H46" t="n">
         <v>1.025</v>
       </c>
-      <c r="H46" t="n">
+      <c r="I46" t="n">
         <v>0.6525</v>
       </c>
     </row>
@@ -1838,15 +1978,18 @@
         <v>-9.7e-05</v>
       </c>
       <c r="E47" t="n">
-        <v>-29.0068</v>
+        <v>-29.01</v>
       </c>
       <c r="F47" t="n">
+        <v>-56.66</v>
+      </c>
+      <c r="G47" t="n">
         <v>0.3875</v>
       </c>
-      <c r="G47" t="n">
+      <c r="H47" t="n">
         <v>1.134</v>
       </c>
-      <c r="H47" t="n">
+      <c r="I47" t="n">
         <v>0.6049</v>
       </c>
     </row>
@@ -1868,15 +2011,18 @@
         <v>9e-06</v>
       </c>
       <c r="E48" t="n">
-        <v>2.7949</v>
+        <v>2.79</v>
       </c>
       <c r="F48" t="n">
+        <v>-24.86</v>
+      </c>
+      <c r="G48" t="n">
         <v>0.7371</v>
       </c>
-      <c r="G48" t="n">
+      <c r="H48" t="n">
         <v>1.307</v>
       </c>
-      <c r="H48" t="n">
+      <c r="I48" t="n">
         <v>1.1687</v>
       </c>
     </row>
@@ -1901,12 +2047,15 @@
         <v>21.77</v>
       </c>
       <c r="F49" t="n">
+        <v>-5.88</v>
+      </c>
+      <c r="G49" t="n">
         <v>0.4977</v>
       </c>
-      <c r="G49" t="n">
+      <c r="H49" t="n">
         <v>1.041</v>
       </c>
-      <c r="H49" t="n">
+      <c r="I49" t="n">
         <v>0.6685</v>
       </c>
     </row>
@@ -1928,15 +2077,18 @@
         <v>-9.8e-05</v>
       </c>
       <c r="E50" t="n">
-        <v>-29.5136</v>
+        <v>-29.51</v>
       </c>
       <c r="F50" t="n">
+        <v>-57.33</v>
+      </c>
+      <c r="G50" t="n">
         <v>0.3471</v>
       </c>
-      <c r="G50" t="n">
+      <c r="H50" t="n">
         <v>1.111</v>
       </c>
-      <c r="H50" t="n">
+      <c r="I50" t="n">
         <v>0.5417</v>
       </c>
     </row>
@@ -1958,15 +2110,18 @@
         <v>1e-05</v>
       </c>
       <c r="E51" t="n">
-        <v>2.8908</v>
+        <v>2.89</v>
       </c>
       <c r="F51" t="n">
+        <v>-24.93</v>
+      </c>
+      <c r="G51" t="n">
         <v>0.7149</v>
       </c>
-      <c r="G51" t="n">
+      <c r="H51" t="n">
         <v>1.311</v>
       </c>
-      <c r="H51" t="n">
+      <c r="I51" t="n">
         <v>1.1508</v>
       </c>
     </row>
@@ -1991,12 +2146,15 @@
         <v>21.59</v>
       </c>
       <c r="F52" t="n">
+        <v>-6.23</v>
+      </c>
+      <c r="G52" t="n">
         <v>0.4917</v>
       </c>
-      <c r="G52" t="n">
+      <c r="H52" t="n">
         <v>1.052</v>
       </c>
-      <c r="H52" t="n">
+      <c r="I52" t="n">
         <v>0.6801</v>
       </c>
     </row>
@@ -2018,15 +2176,18 @@
         <v>-0.000102</v>
       </c>
       <c r="E53" t="n">
-        <v>-30.6728</v>
+        <v>-30.67</v>
       </c>
       <c r="F53" t="n">
+        <v>-60.16</v>
+      </c>
+      <c r="G53" t="n">
         <v>0.3028</v>
       </c>
-      <c r="G53" t="n">
+      <c r="H53" t="n">
         <v>1.096</v>
       </c>
-      <c r="H53" t="n">
+      <c r="I53" t="n">
         <v>0.469</v>
       </c>
     </row>
@@ -2051,12 +2212,15 @@
         <v>7.66</v>
       </c>
       <c r="F54" t="n">
+        <v>-21.83</v>
+      </c>
+      <c r="G54" t="n">
         <v>0.7614</v>
       </c>
-      <c r="G54" t="n">
+      <c r="H54" t="n">
         <v>1.282</v>
       </c>
-      <c r="H54" t="n">
+      <c r="I54" t="n">
         <v>1.077</v>
       </c>
     </row>
@@ -2081,12 +2245,15 @@
         <v>25.15</v>
       </c>
       <c r="F55" t="n">
+        <v>-4.34</v>
+      </c>
+      <c r="G55" t="n">
         <v>0.5489000000000001</v>
       </c>
-      <c r="G55" t="n">
+      <c r="H55" t="n">
         <v>1.07</v>
       </c>
-      <c r="H55" t="n">
+      <c r="I55" t="n">
         <v>0.6982</v>
       </c>
     </row>
@@ -2108,15 +2275,18 @@
         <v>-0.000108</v>
       </c>
       <c r="E56" t="n">
-        <v>-32.2395</v>
+        <v>-32.24</v>
       </c>
       <c r="F56" t="n">
+        <v>-61.75</v>
+      </c>
+      <c r="G56" t="n">
         <v>0.2979</v>
       </c>
-      <c r="G56" t="n">
+      <c r="H56" t="n">
         <v>1.046</v>
       </c>
-      <c r="H56" t="n">
+      <c r="I56" t="n">
         <v>0.4257</v>
       </c>
     </row>
@@ -2138,15 +2308,18 @@
         <v>2.1e-05</v>
       </c>
       <c r="E57" t="n">
-        <v>6.2449</v>
+        <v>6.24</v>
       </c>
       <c r="F57" t="n">
+        <v>-23.27</v>
+      </c>
+      <c r="G57" t="n">
         <v>0.7348</v>
       </c>
-      <c r="G57" t="n">
+      <c r="H57" t="n">
         <v>1.307</v>
       </c>
-      <c r="H57" t="n">
+      <c r="I57" t="n">
         <v>1.0736</v>
       </c>
     </row>
@@ -2171,13 +2344,313 @@
         <v>24.07</v>
       </c>
       <c r="F58" t="n">
+        <v>-5.44</v>
+      </c>
+      <c r="G58" t="n">
         <v>0.5484</v>
       </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
         <v>1.126</v>
       </c>
-      <c r="H58" t="n">
+      <c r="I58" t="n">
         <v>0.7531</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Septiembre 14-2026</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Emisión Azul Hα</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>6562.115</v>
+      </c>
+      <c r="D59" t="n">
+        <v>-0.000106</v>
+      </c>
+      <c r="E59" t="n">
+        <v>-31.84</v>
+      </c>
+      <c r="F59" t="n">
+        <v>-60.8</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.3328</v>
+      </c>
+      <c r="H59" t="n">
+        <v>1.182</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.6012</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Septiembre 14-2026</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Absorción Hα</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>6562.933</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1.8e-05</v>
+      </c>
+      <c r="E60" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="F60" t="n">
+        <v>-23.45</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0.7742</v>
+      </c>
+      <c r="H60" t="n">
+        <v>1.307</v>
+      </c>
+      <c r="I60" t="n">
+        <v>1.1705</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Septiembre 14-2026</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Absorción Cobalto</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>6563.914</v>
+      </c>
+      <c r="D61" t="n">
+        <v>7.9e-05</v>
+      </c>
+      <c r="E61" t="n">
+        <v>23.63</v>
+      </c>
+      <c r="F61" t="n">
+        <v>-5.33</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.5512</v>
+      </c>
+      <c r="H61" t="n">
+        <v>1.131</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.7586000000000001</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Septiembre 21-2026</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Emisión Azul Hα</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>6562.034</v>
+      </c>
+      <c r="D62" t="n">
+        <v>-0.000119</v>
+      </c>
+      <c r="E62" t="n">
+        <v>-35.54</v>
+      </c>
+      <c r="F62" t="n">
+        <v>-63.75</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0.7144</v>
+      </c>
+      <c r="H62" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.8494</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Septiembre 21-2026</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Absorción Hα</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>6562.634</v>
+      </c>
+      <c r="D63" t="n">
+        <v>-2.7e-05</v>
+      </c>
+      <c r="E63" t="n">
+        <v>-8.140000000000001</v>
+      </c>
+      <c r="F63" t="n">
+        <v>-36.35</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0.8189</v>
+      </c>
+      <c r="H63" t="n">
+        <v>1.818</v>
+      </c>
+      <c r="I63" t="n">
+        <v>1.6087</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Septiembre 21-2026</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Absorción Cobalto</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>6563.894</v>
+      </c>
+      <c r="D64" t="n">
+        <v>7.6e-05</v>
+      </c>
+      <c r="E64" t="n">
+        <v>22.71</v>
+      </c>
+      <c r="F64" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0.5586</v>
+      </c>
+      <c r="H64" t="n">
+        <v>1.121</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.7483</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Septiembre 29-2026</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Emisión Azul Hα</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>6562.069</v>
+      </c>
+      <c r="D65" t="n">
+        <v>-0.000113</v>
+      </c>
+      <c r="E65" t="n">
+        <v>-33.92</v>
+      </c>
+      <c r="F65" t="n">
+        <v>-60.5</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0.5419</v>
+      </c>
+      <c r="H65" t="n">
+        <v>1.044</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0.7276</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Septiembre 29-2026</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Absorción Hα</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>6562.752</v>
+      </c>
+      <c r="D66" t="n">
+        <v>-9e-06</v>
+      </c>
+      <c r="E66" t="n">
+        <v>-2.76</v>
+      </c>
+      <c r="F66" t="n">
+        <v>-29.34</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0.8161</v>
+      </c>
+      <c r="H66" t="n">
+        <v>1.538</v>
+      </c>
+      <c r="I66" t="n">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Septiembre 29-2026</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Absorción Cobalto</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>6563.856</v>
+      </c>
+      <c r="D67" t="n">
+        <v>6.999999999999999e-05</v>
+      </c>
+      <c r="E67" t="n">
+        <v>20.95</v>
+      </c>
+      <c r="F67" t="n">
+        <v>-5.63</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0.5543</v>
+      </c>
+      <c r="H67" t="n">
+        <v>1.133</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0.7606000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/Datos ESPARTACO/Parámetros para análisis de Antares/resultados perfiles halpha 2024, 2025 y 2026.xlsx
+++ b/Datos ESPARTACO/Parámetros para análisis de Antares/resultados perfiles halpha 2024, 2025 y 2026.xlsx
@@ -487,25 +487,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6562.448</v>
+        <v>6562.187</v>
       </c>
       <c r="D2" t="n">
-        <v>-5.5e-05</v>
+        <v>-9.500000000000001e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>-16.64</v>
+        <v>-28.55</v>
       </c>
       <c r="F2" t="n">
-        <v>-35.29</v>
+        <v>-47.2</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3898</v>
+        <v>0.2849</v>
       </c>
       <c r="H2" t="n">
-        <v>1.555</v>
+        <v>1.36</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9323</v>
+        <v>0.5462</v>
       </c>
     </row>
     <row r="3">
@@ -520,25 +520,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6562.905</v>
+        <v>6562.913</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4e-05</v>
+        <v>1.5e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>4.24</v>
+        <v>4.61</v>
       </c>
       <c r="F3" t="n">
-        <v>-14.41</v>
+        <v>-14.04</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9122</v>
+        <v>0.7577</v>
       </c>
       <c r="H3" t="n">
-        <v>1.059</v>
+        <v>1.012</v>
       </c>
       <c r="I3" t="n">
-        <v>1.1795</v>
+        <v>0.9297</v>
       </c>
     </row>
     <row r="4">
@@ -553,25 +553,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6563.815</v>
+        <v>6563.814</v>
       </c>
       <c r="D4" t="n">
         <v>6.4e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>19.1</v>
+        <v>19.04</v>
       </c>
       <c r="F4" t="n">
-        <v>0.45</v>
+        <v>0.39</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4944</v>
+        <v>0.4981</v>
       </c>
       <c r="H4" t="n">
-        <v>0.927</v>
+        <v>0.904</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5872000000000001</v>
+        <v>0.5735</v>
       </c>
     </row>
     <row r="5">
@@ -586,25 +586,25 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6561.996</v>
+        <v>6561.995</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.000124</v>
+        <v>-0.000125</v>
       </c>
       <c r="E5" t="n">
-        <v>-37.28</v>
+        <v>-37.33</v>
       </c>
       <c r="F5" t="n">
-        <v>-59.8</v>
+        <v>-59.85</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1879</v>
+        <v>0.1877</v>
       </c>
       <c r="H5" t="n">
-        <v>0.982</v>
+        <v>0.981</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2444</v>
+        <v>0.243</v>
       </c>
     </row>
     <row r="6">
@@ -619,25 +619,25 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6563.038</v>
+        <v>6563.039</v>
       </c>
       <c r="D6" t="n">
-        <v>3.4e-05</v>
+        <v>3.5e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>10.34</v>
+        <v>10.35</v>
       </c>
       <c r="F6" t="n">
-        <v>-12.18</v>
+        <v>-12.17</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6215000000000001</v>
+        <v>0.6212</v>
       </c>
       <c r="H6" t="n">
-        <v>0.875</v>
+        <v>0.874</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6232</v>
+        <v>0.6226</v>
       </c>
     </row>
     <row r="7">
@@ -670,7 +670,7 @@
         <v>0.883</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5611</v>
+        <v>0.5610000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -685,25 +685,25 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6562.542</v>
+        <v>6562.391</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.1e-05</v>
+        <v>-6.4e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>-12.35</v>
+        <v>-19.22</v>
       </c>
       <c r="F8" t="n">
-        <v>-40.69</v>
+        <v>-47.56</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5289</v>
+        <v>0.3317</v>
       </c>
       <c r="H8" t="n">
-        <v>1.223</v>
+        <v>1.214</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9347</v>
+        <v>0.5911</v>
       </c>
     </row>
     <row r="9">
@@ -718,25 +718,25 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6563.025</v>
+        <v>6563.101</v>
       </c>
       <c r="D9" t="n">
-        <v>3.2e-05</v>
+        <v>4.4e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>9.720000000000001</v>
+        <v>13.19</v>
       </c>
       <c r="F9" t="n">
-        <v>-18.62</v>
+        <v>-15.15</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9089</v>
+        <v>0.7374000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>1.164</v>
+        <v>1.09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.309</v>
+        <v>0.9929</v>
       </c>
     </row>
     <row r="10">
@@ -763,7 +763,7 @@
         <v>-0.87</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4879</v>
+        <v>0.4888</v>
       </c>
       <c r="H10" t="n">
         <v>0.926</v>
@@ -784,25 +784,25 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6562.498</v>
+        <v>6562.446</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.8e-05</v>
+        <v>-5.6e-05</v>
       </c>
       <c r="E11" t="n">
-        <v>-14.35</v>
+        <v>-16.7</v>
       </c>
       <c r="F11" t="n">
-        <v>-43.7</v>
+        <v>-46.05</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5451</v>
+        <v>0.4656</v>
       </c>
       <c r="H11" t="n">
-        <v>1.117</v>
+        <v>1.108</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8788</v>
+        <v>0.7116</v>
       </c>
     </row>
     <row r="12">
@@ -817,25 +817,25 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6563.045</v>
+        <v>6563.069</v>
       </c>
       <c r="D12" t="n">
-        <v>3.5e-05</v>
+        <v>3.9e-05</v>
       </c>
       <c r="E12" t="n">
-        <v>10.64</v>
+        <v>11.76</v>
       </c>
       <c r="F12" t="n">
-        <v>-18.71</v>
+        <v>-17.59</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9061</v>
+        <v>0.8393</v>
       </c>
       <c r="H12" t="n">
-        <v>1.208</v>
+        <v>1.182</v>
       </c>
       <c r="I12" t="n">
-        <v>1.2492</v>
+        <v>1.1297</v>
       </c>
     </row>
     <row r="13">
@@ -862,13 +862,13 @@
         <v>-0.66</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5288</v>
+        <v>0.5301</v>
       </c>
       <c r="H13" t="n">
-        <v>0.968</v>
+        <v>0.958</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6183</v>
+        <v>0.6122</v>
       </c>
     </row>
     <row r="14">
@@ -883,25 +883,25 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6562.495</v>
+        <v>6562.32</v>
       </c>
       <c r="D14" t="n">
-        <v>-4.8e-05</v>
+        <v>-7.499999999999999e-05</v>
       </c>
       <c r="E14" t="n">
-        <v>-14.47</v>
+        <v>-22.47</v>
       </c>
       <c r="F14" t="n">
-        <v>-44.04</v>
+        <v>-52.04</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3796</v>
+        <v>0.2589</v>
       </c>
       <c r="H14" t="n">
-        <v>1.317</v>
+        <v>1.341</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8424</v>
+        <v>0.4988</v>
       </c>
     </row>
     <row r="15">
@@ -916,25 +916,25 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6563.104</v>
+        <v>6563.15</v>
       </c>
       <c r="D15" t="n">
-        <v>4.5e-05</v>
+        <v>5.1e-05</v>
       </c>
       <c r="E15" t="n">
-        <v>13.36</v>
+        <v>15.42</v>
       </c>
       <c r="F15" t="n">
-        <v>-16.21</v>
+        <v>-14.15</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7659</v>
+        <v>0.6791</v>
       </c>
       <c r="H15" t="n">
-        <v>1.175</v>
+        <v>1.078</v>
       </c>
       <c r="I15" t="n">
-        <v>1.1158</v>
+        <v>0.9015</v>
       </c>
     </row>
     <row r="16">
@@ -961,13 +961,13 @@
         <v>-0.8100000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4869</v>
+        <v>0.4903</v>
       </c>
       <c r="H16" t="n">
-        <v>1.008</v>
+        <v>0.973</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6425999999999999</v>
+        <v>0.6217</v>
       </c>
     </row>
     <row r="17">
@@ -982,25 +982,25 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6562.365</v>
+        <v>6562.254</v>
       </c>
       <c r="D17" t="n">
-        <v>-6.8e-05</v>
+        <v>-8.500000000000001e-05</v>
       </c>
       <c r="E17" t="n">
-        <v>-20.43</v>
+        <v>-25.49</v>
       </c>
       <c r="F17" t="n">
-        <v>-48.81</v>
+        <v>-53.87</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2681</v>
+        <v>0.2312</v>
       </c>
       <c r="H17" t="n">
-        <v>1.281</v>
+        <v>1.177</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4125</v>
+        <v>0.327</v>
       </c>
     </row>
     <row r="18">
@@ -1015,25 +1015,25 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6563.101</v>
+        <v>6563.129</v>
       </c>
       <c r="D18" t="n">
-        <v>4.4e-05</v>
+        <v>4.8e-05</v>
       </c>
       <c r="E18" t="n">
-        <v>13.2</v>
+        <v>14.49</v>
       </c>
       <c r="F18" t="n">
-        <v>-15.18</v>
+        <v>-13.89</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6959</v>
+        <v>0.6444</v>
       </c>
       <c r="H18" t="n">
-        <v>1.095</v>
+        <v>1.072</v>
       </c>
       <c r="I18" t="n">
-        <v>0.915</v>
+        <v>0.8299</v>
       </c>
     </row>
     <row r="19">
@@ -1063,10 +1063,10 @@
         <v>0.5024999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>1.002</v>
+        <v>1.003</v>
       </c>
       <c r="I19" t="n">
-        <v>0.639</v>
+        <v>0.6393</v>
       </c>
     </row>
     <row r="20">
@@ -1081,25 +1081,25 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>6562.444</v>
+        <v>6562.396</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.6e-05</v>
+        <v>-6.3e-05</v>
       </c>
       <c r="E20" t="n">
-        <v>-16.8</v>
+        <v>-18.99</v>
       </c>
       <c r="F20" t="n">
-        <v>-44.29</v>
+        <v>-46.48</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4913</v>
+        <v>0.4129</v>
       </c>
       <c r="H20" t="n">
-        <v>1.14</v>
+        <v>1.111</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7803</v>
+        <v>0.6548</v>
       </c>
     </row>
     <row r="21">
@@ -1114,25 +1114,25 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>6562.999</v>
+        <v>6563.039</v>
       </c>
       <c r="D21" t="n">
-        <v>2.8e-05</v>
+        <v>3.5e-05</v>
       </c>
       <c r="E21" t="n">
-        <v>8.539999999999999</v>
+        <v>10.38</v>
       </c>
       <c r="F21" t="n">
-        <v>-18.95</v>
+        <v>-17.11</v>
       </c>
       <c r="G21" t="n">
-        <v>0.7731</v>
+        <v>0.7056</v>
       </c>
       <c r="H21" t="n">
-        <v>1.268</v>
+        <v>1.246</v>
       </c>
       <c r="I21" t="n">
-        <v>1.1841</v>
+        <v>1.062</v>
       </c>
     </row>
     <row r="22">
@@ -1180,25 +1180,25 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>6562.389</v>
+        <v>6562.36</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.499999999999999e-05</v>
+        <v>-6.9e-05</v>
       </c>
       <c r="E23" t="n">
-        <v>-19.34</v>
+        <v>-20.65</v>
       </c>
       <c r="F23" t="n">
-        <v>-45.36</v>
+        <v>-46.67</v>
       </c>
       <c r="G23" t="n">
-        <v>0.4258</v>
+        <v>0.3915</v>
       </c>
       <c r="H23" t="n">
-        <v>1.119</v>
+        <v>1.1</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5682</v>
+        <v>0.5137</v>
       </c>
     </row>
     <row r="24">
@@ -1213,25 +1213,25 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>6563.008</v>
+        <v>6563.027</v>
       </c>
       <c r="D24" t="n">
-        <v>3e-05</v>
+        <v>3.3e-05</v>
       </c>
       <c r="E24" t="n">
-        <v>8.93</v>
+        <v>9.83</v>
       </c>
       <c r="F24" t="n">
-        <v>-17.09</v>
+        <v>-16.19</v>
       </c>
       <c r="G24" t="n">
-        <v>0.7266</v>
+        <v>0.6941000000000001</v>
       </c>
       <c r="H24" t="n">
-        <v>1.234</v>
+        <v>1.226</v>
       </c>
       <c r="I24" t="n">
-        <v>1.069</v>
+        <v>1.0146</v>
       </c>
     </row>
     <row r="25">
@@ -1279,25 +1279,25 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>6562.299</v>
+        <v>6562.282</v>
       </c>
       <c r="D26" t="n">
-        <v>-7.8e-05</v>
+        <v>-8.1e-05</v>
       </c>
       <c r="E26" t="n">
-        <v>-23.45</v>
+        <v>-24.22</v>
       </c>
       <c r="F26" t="n">
-        <v>-46.56</v>
+        <v>-47.33</v>
       </c>
       <c r="G26" t="n">
-        <v>0.4244</v>
+        <v>0.387</v>
       </c>
       <c r="H26" t="n">
-        <v>1.264</v>
+        <v>1.261</v>
       </c>
       <c r="I26" t="n">
-        <v>0.7702</v>
+        <v>0.6253</v>
       </c>
     </row>
     <row r="27">
@@ -1312,25 +1312,25 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>6562.986</v>
+        <v>6562.989</v>
       </c>
       <c r="D27" t="n">
-        <v>2.6e-05</v>
+        <v>2.7e-05</v>
       </c>
       <c r="E27" t="n">
-        <v>7.94</v>
+        <v>8.09</v>
       </c>
       <c r="F27" t="n">
-        <v>-15.17</v>
+        <v>-15.02</v>
       </c>
       <c r="G27" t="n">
-        <v>0.825</v>
+        <v>0.7983</v>
       </c>
       <c r="H27" t="n">
-        <v>1.177</v>
+        <v>1.143</v>
       </c>
       <c r="I27" t="n">
-        <v>1.2804</v>
+        <v>1.1694</v>
       </c>
     </row>
     <row r="28">
@@ -1357,13 +1357,13 @@
         <v>-0.47</v>
       </c>
       <c r="G28" t="n">
-        <v>0.5544</v>
+        <v>0.5558</v>
       </c>
       <c r="H28" t="n">
-        <v>1.053</v>
+        <v>1.056</v>
       </c>
       <c r="I28" t="n">
-        <v>0.6811</v>
+        <v>0.6843</v>
       </c>
     </row>
     <row r="29">
@@ -1378,25 +1378,25 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>6562.212</v>
+        <v>6562.24</v>
       </c>
       <c r="D29" t="n">
-        <v>-9.1e-05</v>
+        <v>-8.7e-05</v>
       </c>
       <c r="E29" t="n">
-        <v>-27.43</v>
+        <v>-26.12</v>
       </c>
       <c r="F29" t="n">
-        <v>-48.48</v>
+        <v>-47.17</v>
       </c>
       <c r="G29" t="n">
-        <v>0.3821</v>
+        <v>0.392</v>
       </c>
       <c r="H29" t="n">
-        <v>1.244</v>
+        <v>1.248</v>
       </c>
       <c r="I29" t="n">
-        <v>0.6911</v>
+        <v>0.629</v>
       </c>
     </row>
     <row r="30">
@@ -1411,25 +1411,25 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>6562.939</v>
+        <v>6562.919</v>
       </c>
       <c r="D30" t="n">
-        <v>1.9e-05</v>
+        <v>1.6e-05</v>
       </c>
       <c r="E30" t="n">
-        <v>5.82</v>
+        <v>4.89</v>
       </c>
       <c r="F30" t="n">
-        <v>-15.23</v>
+        <v>-16.16</v>
       </c>
       <c r="G30" t="n">
-        <v>0.7957</v>
+        <v>0.8025</v>
       </c>
       <c r="H30" t="n">
-        <v>1.154</v>
+        <v>1.157</v>
       </c>
       <c r="I30" t="n">
-        <v>1.1765</v>
+        <v>1.1408</v>
       </c>
     </row>
     <row r="31">
@@ -1456,13 +1456,13 @@
         <v>-0.8</v>
       </c>
       <c r="G31" t="n">
-        <v>0.5538</v>
+        <v>0.555</v>
       </c>
       <c r="H31" t="n">
-        <v>1.043</v>
+        <v>1.05</v>
       </c>
       <c r="I31" t="n">
-        <v>0.6707</v>
+        <v>0.6783</v>
       </c>
     </row>
     <row r="32">
@@ -1477,25 +1477,25 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>6562.21</v>
+        <v>6562.184</v>
       </c>
       <c r="D32" t="n">
-        <v>-9.2e-05</v>
+        <v>-9.6e-05</v>
       </c>
       <c r="E32" t="n">
-        <v>-27.5</v>
+        <v>-28.69</v>
       </c>
       <c r="F32" t="n">
-        <v>-48.22</v>
+        <v>-49.41</v>
       </c>
       <c r="G32" t="n">
-        <v>0.3988</v>
+        <v>0.345</v>
       </c>
       <c r="H32" t="n">
-        <v>1.093</v>
+        <v>1.101</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5226</v>
+        <v>0.4551</v>
       </c>
     </row>
     <row r="33">
@@ -1510,25 +1510,25 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>6562.873</v>
+        <v>6562.908</v>
       </c>
       <c r="D33" t="n">
-        <v>9e-06</v>
+        <v>1.5e-05</v>
       </c>
       <c r="E33" t="n">
-        <v>2.76</v>
+        <v>4.37</v>
       </c>
       <c r="F33" t="n">
-        <v>-17.96</v>
+        <v>-16.35</v>
       </c>
       <c r="G33" t="n">
-        <v>0.6762</v>
+        <v>0.6516</v>
       </c>
       <c r="H33" t="n">
-        <v>1.252</v>
+        <v>1.206</v>
       </c>
       <c r="I33" t="n">
-        <v>1.0153</v>
+        <v>0.9522</v>
       </c>
     </row>
     <row r="34">
@@ -1555,7 +1555,7 @@
         <v>-0.92</v>
       </c>
       <c r="G34" t="n">
-        <v>0.5034999999999999</v>
+        <v>0.5037</v>
       </c>
       <c r="H34" t="n">
         <v>1.025</v>
@@ -1582,19 +1582,19 @@
         <v>-0.000107</v>
       </c>
       <c r="E35" t="n">
-        <v>-32.01</v>
+        <v>-32</v>
       </c>
       <c r="F35" t="n">
-        <v>-50.44</v>
+        <v>-50.43</v>
       </c>
       <c r="G35" t="n">
-        <v>0.3881</v>
+        <v>0.5853</v>
       </c>
       <c r="H35" t="n">
-        <v>1.063</v>
+        <v>1.013</v>
       </c>
       <c r="I35" t="n">
-        <v>0.4802</v>
+        <v>0.6923</v>
       </c>
     </row>
     <row r="36">
@@ -1609,25 +1609,25 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>6562.878</v>
+        <v>6562.735</v>
       </c>
       <c r="D36" t="n">
-        <v>1e-05</v>
+        <v>-1.2e-05</v>
       </c>
       <c r="E36" t="n">
-        <v>3.02</v>
+        <v>-3.51</v>
       </c>
       <c r="F36" t="n">
-        <v>-15.41</v>
+        <v>-21.94</v>
       </c>
       <c r="G36" t="n">
-        <v>0.641</v>
+        <v>0.657</v>
       </c>
       <c r="H36" t="n">
-        <v>1.231</v>
+        <v>1.531</v>
       </c>
       <c r="I36" t="n">
-        <v>1.0231</v>
+        <v>1.1751</v>
       </c>
     </row>
     <row r="37">
@@ -1654,13 +1654,13 @@
         <v>-0.5600000000000001</v>
       </c>
       <c r="G37" t="n">
-        <v>0.5184</v>
+        <v>0.5172</v>
       </c>
       <c r="H37" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="I37" t="n">
-        <v>0.6683</v>
+        <v>0.6977</v>
       </c>
     </row>
     <row r="38">
@@ -1675,25 +1675,25 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>6562.019</v>
+        <v>6561.993</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.000121</v>
+        <v>-0.000125</v>
       </c>
       <c r="E38" t="n">
-        <v>-36.24</v>
+        <v>-37.43</v>
       </c>
       <c r="F38" t="n">
-        <v>-59.37</v>
+        <v>-60.56</v>
       </c>
       <c r="G38" t="n">
-        <v>0.269</v>
+        <v>0.2545</v>
       </c>
       <c r="H38" t="n">
-        <v>1.081</v>
+        <v>1.065</v>
       </c>
       <c r="I38" t="n">
-        <v>0.4337</v>
+        <v>0.4065</v>
       </c>
     </row>
     <row r="39">
@@ -1708,25 +1708,25 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>6562.853</v>
+        <v>6562.864</v>
       </c>
       <c r="D39" t="n">
-        <v>6e-06</v>
+        <v>8e-06</v>
       </c>
       <c r="E39" t="n">
-        <v>1.87</v>
+        <v>2.39</v>
       </c>
       <c r="F39" t="n">
-        <v>-21.26</v>
+        <v>-20.74</v>
       </c>
       <c r="G39" t="n">
-        <v>0.6818</v>
+        <v>0.6723</v>
       </c>
       <c r="H39" t="n">
-        <v>1.214</v>
+        <v>1.2</v>
       </c>
       <c r="I39" t="n">
-        <v>1.0234</v>
+        <v>0.9969</v>
       </c>
     </row>
     <row r="40">
@@ -1756,10 +1756,10 @@
         <v>0.4884</v>
       </c>
       <c r="H40" t="n">
-        <v>1.025</v>
+        <v>1.026</v>
       </c>
       <c r="I40" t="n">
-        <v>0.6531</v>
+        <v>0.6538</v>
       </c>
     </row>
     <row r="41">
@@ -1774,25 +1774,25 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>6561.891</v>
+        <v>6561.89</v>
       </c>
       <c r="D41" t="n">
         <v>-0.00014</v>
       </c>
       <c r="E41" t="n">
-        <v>-42.06</v>
+        <v>-42.1</v>
       </c>
       <c r="F41" t="n">
-        <v>-65.98999999999999</v>
+        <v>-66.03</v>
       </c>
       <c r="G41" t="n">
-        <v>0.2086</v>
+        <v>0.2088</v>
       </c>
       <c r="H41" t="n">
-        <v>0.959</v>
+        <v>0.96</v>
       </c>
       <c r="I41" t="n">
-        <v>0.2413</v>
+        <v>0.2419</v>
       </c>
     </row>
     <row r="42">
@@ -1819,13 +1819,13 @@
         <v>-20.4</v>
       </c>
       <c r="G42" t="n">
-        <v>0.6597</v>
+        <v>0.6605</v>
       </c>
       <c r="H42" t="n">
         <v>1.13</v>
       </c>
       <c r="I42" t="n">
-        <v>0.9416</v>
+        <v>0.9446</v>
       </c>
     </row>
     <row r="43">
@@ -1855,10 +1855,10 @@
         <v>0.5004</v>
       </c>
       <c r="H43" t="n">
-        <v>1.027</v>
+        <v>1.025</v>
       </c>
       <c r="I43" t="n">
-        <v>0.6543</v>
+        <v>0.6525</v>
       </c>
     </row>
     <row r="44">
@@ -1873,25 +1873,25 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>6562.148</v>
+        <v>6561.993</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.000101</v>
+        <v>-0.000125</v>
       </c>
       <c r="E44" t="n">
-        <v>-30.35</v>
+        <v>-37.42</v>
       </c>
       <c r="F44" t="n">
-        <v>-56.85</v>
+        <v>-63.92</v>
       </c>
       <c r="G44" t="n">
-        <v>0.3547</v>
+        <v>0.2188</v>
       </c>
       <c r="H44" t="n">
-        <v>1.051</v>
+        <v>0.924</v>
       </c>
       <c r="I44" t="n">
-        <v>0.4543</v>
+        <v>0.2463</v>
       </c>
     </row>
     <row r="45">
@@ -1906,25 +1906,25 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>6562.842</v>
+        <v>6562.95</v>
       </c>
       <c r="D45" t="n">
-        <v>5e-06</v>
+        <v>2.1e-05</v>
       </c>
       <c r="E45" t="n">
-        <v>1.35</v>
+        <v>6.3</v>
       </c>
       <c r="F45" t="n">
-        <v>-25.15</v>
+        <v>-20.2</v>
       </c>
       <c r="G45" t="n">
-        <v>0.716</v>
+        <v>0.6398</v>
       </c>
       <c r="H45" t="n">
-        <v>1.293</v>
+        <v>1.174</v>
       </c>
       <c r="I45" t="n">
-        <v>1.128</v>
+        <v>0.9154</v>
       </c>
     </row>
     <row r="46">
@@ -1951,7 +1951,7 @@
         <v>-5.86</v>
       </c>
       <c r="G46" t="n">
-        <v>0.4954</v>
+        <v>0.4953</v>
       </c>
       <c r="H46" t="n">
         <v>1.025</v>
@@ -1972,25 +1972,25 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>6562.177</v>
+        <v>6562.1</v>
       </c>
       <c r="D47" t="n">
-        <v>-9.7e-05</v>
+        <v>-0.000109</v>
       </c>
       <c r="E47" t="n">
-        <v>-29.01</v>
+        <v>-32.54</v>
       </c>
       <c r="F47" t="n">
-        <v>-56.66</v>
+        <v>-60.19</v>
       </c>
       <c r="G47" t="n">
-        <v>0.3875</v>
+        <v>0.3017</v>
       </c>
       <c r="H47" t="n">
-        <v>1.134</v>
+        <v>1.091</v>
       </c>
       <c r="I47" t="n">
-        <v>0.6049</v>
+        <v>0.4608</v>
       </c>
     </row>
     <row r="48">
@@ -2005,25 +2005,25 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>6562.873</v>
+        <v>6562.93</v>
       </c>
       <c r="D48" t="n">
-        <v>9e-06</v>
+        <v>1.8e-05</v>
       </c>
       <c r="E48" t="n">
-        <v>2.79</v>
+        <v>5.41</v>
       </c>
       <c r="F48" t="n">
-        <v>-24.86</v>
+        <v>-22.24</v>
       </c>
       <c r="G48" t="n">
-        <v>0.7371</v>
+        <v>0.6808999999999999</v>
       </c>
       <c r="H48" t="n">
-        <v>1.307</v>
+        <v>1.248</v>
       </c>
       <c r="I48" t="n">
-        <v>1.1687</v>
+        <v>1.0301</v>
       </c>
     </row>
     <row r="49">
@@ -2050,7 +2050,7 @@
         <v>-5.88</v>
       </c>
       <c r="G49" t="n">
-        <v>0.4977</v>
+        <v>0.4979</v>
       </c>
       <c r="H49" t="n">
         <v>1.041</v>
@@ -2071,25 +2071,25 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>6562.166</v>
+        <v>6562.031</v>
       </c>
       <c r="D50" t="n">
-        <v>-9.8e-05</v>
+        <v>-0.000119</v>
       </c>
       <c r="E50" t="n">
-        <v>-29.51</v>
+        <v>-35.67</v>
       </c>
       <c r="F50" t="n">
-        <v>-57.33</v>
+        <v>-63.49</v>
       </c>
       <c r="G50" t="n">
-        <v>0.3471</v>
+        <v>0.2329</v>
       </c>
       <c r="H50" t="n">
-        <v>1.111</v>
+        <v>1.038</v>
       </c>
       <c r="I50" t="n">
-        <v>0.5417</v>
+        <v>0.3587</v>
       </c>
     </row>
     <row r="51">
@@ -2104,25 +2104,25 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>6562.875</v>
+        <v>6562.96</v>
       </c>
       <c r="D51" t="n">
-        <v>1e-05</v>
+        <v>2.3e-05</v>
       </c>
       <c r="E51" t="n">
-        <v>2.89</v>
+        <v>6.76</v>
       </c>
       <c r="F51" t="n">
-        <v>-24.93</v>
+        <v>-21.06</v>
       </c>
       <c r="G51" t="n">
-        <v>0.7149</v>
+        <v>0.6544</v>
       </c>
       <c r="H51" t="n">
-        <v>1.311</v>
+        <v>1.203</v>
       </c>
       <c r="I51" t="n">
-        <v>1.1508</v>
+        <v>0.9794</v>
       </c>
     </row>
     <row r="52">
@@ -2149,13 +2149,13 @@
         <v>-6.23</v>
       </c>
       <c r="G52" t="n">
-        <v>0.4917</v>
+        <v>0.4919</v>
       </c>
       <c r="H52" t="n">
-        <v>1.052</v>
+        <v>1.046</v>
       </c>
       <c r="I52" t="n">
-        <v>0.6801</v>
+        <v>0.6741</v>
       </c>
     </row>
     <row r="53">
@@ -2170,25 +2170,25 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>6562.141</v>
+        <v>6562.099</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.000102</v>
+        <v>-0.000109</v>
       </c>
       <c r="E53" t="n">
-        <v>-30.67</v>
+        <v>-32.59</v>
       </c>
       <c r="F53" t="n">
-        <v>-60.16</v>
+        <v>-62.08</v>
       </c>
       <c r="G53" t="n">
-        <v>0.3028</v>
+        <v>0.2755</v>
       </c>
       <c r="H53" t="n">
-        <v>1.096</v>
+        <v>1.067</v>
       </c>
       <c r="I53" t="n">
-        <v>0.469</v>
+        <v>0.3939</v>
       </c>
     </row>
     <row r="54">
@@ -2203,25 +2203,25 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>6562.98</v>
+        <v>6562.994</v>
       </c>
       <c r="D54" t="n">
-        <v>2.6e-05</v>
+        <v>2.8e-05</v>
       </c>
       <c r="E54" t="n">
-        <v>7.66</v>
+        <v>8.31</v>
       </c>
       <c r="F54" t="n">
-        <v>-21.83</v>
+        <v>-21.18</v>
       </c>
       <c r="G54" t="n">
-        <v>0.7614</v>
+        <v>0.7407</v>
       </c>
       <c r="H54" t="n">
-        <v>1.282</v>
+        <v>1.259</v>
       </c>
       <c r="I54" t="n">
-        <v>1.077</v>
+        <v>1.0243</v>
       </c>
     </row>
     <row r="55">
@@ -2248,13 +2248,13 @@
         <v>-4.34</v>
       </c>
       <c r="G55" t="n">
-        <v>0.5489000000000001</v>
+        <v>0.5496</v>
       </c>
       <c r="H55" t="n">
-        <v>1.07</v>
+        <v>1.068</v>
       </c>
       <c r="I55" t="n">
-        <v>0.6982</v>
+        <v>0.6957</v>
       </c>
     </row>
     <row r="56">
@@ -2269,25 +2269,25 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>6562.106</v>
+        <v>6562.114</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.000108</v>
+        <v>-0.000106</v>
       </c>
       <c r="E56" t="n">
-        <v>-32.24</v>
+        <v>-31.87</v>
       </c>
       <c r="F56" t="n">
-        <v>-61.75</v>
+        <v>-61.38</v>
       </c>
       <c r="G56" t="n">
-        <v>0.2979</v>
+        <v>0.3095</v>
       </c>
       <c r="H56" t="n">
-        <v>1.046</v>
+        <v>1.04</v>
       </c>
       <c r="I56" t="n">
-        <v>0.4257</v>
+        <v>0.4263</v>
       </c>
     </row>
     <row r="57">
@@ -2302,25 +2302,25 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>6562.949</v>
+        <v>6562.939</v>
       </c>
       <c r="D57" t="n">
-        <v>2.1e-05</v>
+        <v>1.9e-05</v>
       </c>
       <c r="E57" t="n">
-        <v>6.24</v>
+        <v>5.8</v>
       </c>
       <c r="F57" t="n">
-        <v>-23.27</v>
+        <v>-23.71</v>
       </c>
       <c r="G57" t="n">
-        <v>0.7348</v>
+        <v>0.7325</v>
       </c>
       <c r="H57" t="n">
-        <v>1.307</v>
+        <v>1.324</v>
       </c>
       <c r="I57" t="n">
-        <v>1.0736</v>
+        <v>1.0691</v>
       </c>
     </row>
     <row r="58">
@@ -2350,10 +2350,10 @@
         <v>0.5484</v>
       </c>
       <c r="H58" t="n">
-        <v>1.126</v>
+        <v>1.132</v>
       </c>
       <c r="I58" t="n">
-        <v>0.7531</v>
+        <v>0.7595</v>
       </c>
     </row>
     <row r="59">
@@ -2368,25 +2368,25 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>6562.115</v>
+        <v>6562.058</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.000106</v>
+        <v>-0.000115</v>
       </c>
       <c r="E59" t="n">
-        <v>-31.84</v>
+        <v>-34.42</v>
       </c>
       <c r="F59" t="n">
-        <v>-60.8</v>
+        <v>-63.38</v>
       </c>
       <c r="G59" t="n">
-        <v>0.3328</v>
+        <v>0.2949</v>
       </c>
       <c r="H59" t="n">
-        <v>1.182</v>
+        <v>1.058</v>
       </c>
       <c r="I59" t="n">
-        <v>0.6012</v>
+        <v>0.4165</v>
       </c>
     </row>
     <row r="60">
@@ -2401,25 +2401,25 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>6562.933</v>
+        <v>6562.944</v>
       </c>
       <c r="D60" t="n">
-        <v>1.8e-05</v>
+        <v>2e-05</v>
       </c>
       <c r="E60" t="n">
-        <v>5.51</v>
+        <v>6.01</v>
       </c>
       <c r="F60" t="n">
-        <v>-23.45</v>
+        <v>-22.95</v>
       </c>
       <c r="G60" t="n">
-        <v>0.7742</v>
+        <v>0.716</v>
       </c>
       <c r="H60" t="n">
-        <v>1.307</v>
+        <v>1.297</v>
       </c>
       <c r="I60" t="n">
-        <v>1.1705</v>
+        <v>1.0139</v>
       </c>
     </row>
     <row r="61">
@@ -2446,13 +2446,13 @@
         <v>-5.33</v>
       </c>
       <c r="G61" t="n">
-        <v>0.5512</v>
+        <v>0.5528</v>
       </c>
       <c r="H61" t="n">
-        <v>1.131</v>
+        <v>1.149</v>
       </c>
       <c r="I61" t="n">
-        <v>0.7586000000000001</v>
+        <v>0.776</v>
       </c>
     </row>
     <row r="62">
@@ -2479,13 +2479,13 @@
         <v>-63.75</v>
       </c>
       <c r="G62" t="n">
-        <v>0.7144</v>
+        <v>0.7145</v>
       </c>
       <c r="H62" t="n">
         <v>1.1</v>
       </c>
       <c r="I62" t="n">
-        <v>0.8494</v>
+        <v>0.8495</v>
       </c>
     </row>
     <row r="63">
@@ -2518,7 +2518,7 @@
         <v>1.818</v>
       </c>
       <c r="I63" t="n">
-        <v>1.6087</v>
+        <v>1.6089</v>
       </c>
     </row>
     <row r="64">
@@ -2566,25 +2566,25 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>6562.069</v>
+        <v>6562.032</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.000113</v>
+        <v>-0.000119</v>
       </c>
       <c r="E65" t="n">
-        <v>-33.92</v>
+        <v>-35.64</v>
       </c>
       <c r="F65" t="n">
-        <v>-60.5</v>
+        <v>-62.22</v>
       </c>
       <c r="G65" t="n">
-        <v>0.5419</v>
+        <v>0.5748</v>
       </c>
       <c r="H65" t="n">
-        <v>1.044</v>
+        <v>1.027</v>
       </c>
       <c r="I65" t="n">
-        <v>0.7276</v>
+        <v>0.7226</v>
       </c>
     </row>
     <row r="66">
@@ -2599,25 +2599,25 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>6562.752</v>
+        <v>6562.719</v>
       </c>
       <c r="D66" t="n">
-        <v>-9e-06</v>
+        <v>-1.4e-05</v>
       </c>
       <c r="E66" t="n">
-        <v>-2.76</v>
+        <v>-4.23</v>
       </c>
       <c r="F66" t="n">
-        <v>-29.34</v>
+        <v>-30.81</v>
       </c>
       <c r="G66" t="n">
-        <v>0.8161</v>
+        <v>0.7935</v>
       </c>
       <c r="H66" t="n">
-        <v>1.538</v>
+        <v>1.612</v>
       </c>
       <c r="I66" t="n">
-        <v>1.39</v>
+        <v>1.3921</v>
       </c>
     </row>
     <row r="67">
@@ -2644,13 +2644,13 @@
         <v>-5.63</v>
       </c>
       <c r="G67" t="n">
-        <v>0.5543</v>
+        <v>0.5547</v>
       </c>
       <c r="H67" t="n">
-        <v>1.133</v>
+        <v>1.14</v>
       </c>
       <c r="I67" t="n">
-        <v>0.7606000000000001</v>
+        <v>0.7673</v>
       </c>
     </row>
   </sheetData>

--- a/Datos ESPARTACO/Parámetros para análisis de Antares/resultados perfiles halpha 2024, 2025 y 2026.xlsx
+++ b/Datos ESPARTACO/Parámetros para análisis de Antares/resultados perfiles halpha 2024, 2025 y 2026.xlsx
@@ -489,8 +489,10 @@
       <c r="C2" t="n">
         <v>6562.187</v>
       </c>
-      <c r="D2" t="n">
-        <v>-9.500000000000001e-05</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>-9.5e-05</t>
+        </is>
       </c>
       <c r="E2" t="n">
         <v>-28.55</v>
@@ -499,13 +501,13 @@
         <v>-47.2</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2849</v>
+        <v>0.28</v>
       </c>
       <c r="H2" t="n">
         <v>1.36</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5462</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="3">
@@ -522,8 +524,10 @@
       <c r="C3" t="n">
         <v>6562.913</v>
       </c>
-      <c r="D3" t="n">
-        <v>1.5e-05</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1.5e-05</t>
+        </is>
       </c>
       <c r="E3" t="n">
         <v>4.61</v>
@@ -532,13 +536,13 @@
         <v>-14.04</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7577</v>
+        <v>0.76</v>
       </c>
       <c r="H3" t="n">
-        <v>1.012</v>
+        <v>1.01</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9297</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="4">
@@ -555,8 +559,10 @@
       <c r="C4" t="n">
         <v>6563.814</v>
       </c>
-      <c r="D4" t="n">
-        <v>6.4e-05</v>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>6.4e-05</t>
+        </is>
       </c>
       <c r="E4" t="n">
         <v>19.04</v>
@@ -565,13 +571,13 @@
         <v>0.39</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4981</v>
+        <v>0.5</v>
       </c>
       <c r="H4" t="n">
-        <v>0.904</v>
+        <v>0.9</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5735</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="5">
@@ -588,8 +594,10 @@
       <c r="C5" t="n">
         <v>6561.995</v>
       </c>
-      <c r="D5" t="n">
-        <v>-0.000125</v>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>-0.00012</t>
+        </is>
       </c>
       <c r="E5" t="n">
         <v>-37.33</v>
@@ -598,13 +606,13 @@
         <v>-59.85</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1877</v>
+        <v>0.19</v>
       </c>
       <c r="H5" t="n">
-        <v>0.981</v>
+        <v>0.98</v>
       </c>
       <c r="I5" t="n">
-        <v>0.243</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="6">
@@ -621,8 +629,10 @@
       <c r="C6" t="n">
         <v>6563.039</v>
       </c>
-      <c r="D6" t="n">
-        <v>3.5e-05</v>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>3.5e-05</t>
+        </is>
       </c>
       <c r="E6" t="n">
         <v>10.35</v>
@@ -631,13 +641,13 @@
         <v>-12.17</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6212</v>
+        <v>0.62</v>
       </c>
       <c r="H6" t="n">
-        <v>0.874</v>
+        <v>0.87</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6226</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="7">
@@ -654,8 +664,10 @@
       <c r="C7" t="n">
         <v>6563.876</v>
       </c>
-      <c r="D7" t="n">
-        <v>7.3e-05</v>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>7.3e-05</t>
+        </is>
       </c>
       <c r="E7" t="n">
         <v>21.86</v>
@@ -664,13 +676,13 @@
         <v>-0.66</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5265</v>
+        <v>0.53</v>
       </c>
       <c r="H7" t="n">
-        <v>0.883</v>
+        <v>0.88</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -687,8 +699,10 @@
       <c r="C8" t="n">
         <v>6562.391</v>
       </c>
-      <c r="D8" t="n">
-        <v>-6.4e-05</v>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>-6.4e-05</t>
+        </is>
       </c>
       <c r="E8" t="n">
         <v>-19.22</v>
@@ -697,13 +711,13 @@
         <v>-47.56</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3317</v>
+        <v>0.33</v>
       </c>
       <c r="H8" t="n">
-        <v>1.214</v>
+        <v>1.21</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5911</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="9">
@@ -720,8 +734,10 @@
       <c r="C9" t="n">
         <v>6563.101</v>
       </c>
-      <c r="D9" t="n">
-        <v>4.4e-05</v>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>4.4e-05</t>
+        </is>
       </c>
       <c r="E9" t="n">
         <v>13.19</v>
@@ -730,13 +746,13 @@
         <v>-15.15</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7374000000000001</v>
+        <v>0.74</v>
       </c>
       <c r="H9" t="n">
         <v>1.09</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9929</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="10">
@@ -753,8 +769,10 @@
       <c r="C10" t="n">
         <v>6563.998</v>
       </c>
-      <c r="D10" t="n">
-        <v>9.2e-05</v>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>9.2e-05</t>
+        </is>
       </c>
       <c r="E10" t="n">
         <v>27.47</v>
@@ -763,13 +781,13 @@
         <v>-0.87</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4888</v>
+        <v>0.49</v>
       </c>
       <c r="H10" t="n">
-        <v>0.926</v>
+        <v>0.93</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5868</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="11">
@@ -786,8 +804,10 @@
       <c r="C11" t="n">
         <v>6562.446</v>
       </c>
-      <c r="D11" t="n">
-        <v>-5.6e-05</v>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>-5.6e-05</t>
+        </is>
       </c>
       <c r="E11" t="n">
         <v>-16.7</v>
@@ -796,13 +816,13 @@
         <v>-46.05</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4656</v>
+        <v>0.47</v>
       </c>
       <c r="H11" t="n">
-        <v>1.108</v>
+        <v>1.11</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7116</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="12">
@@ -819,8 +839,10 @@
       <c r="C12" t="n">
         <v>6563.069</v>
       </c>
-      <c r="D12" t="n">
-        <v>3.9e-05</v>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>3.9e-05</t>
+        </is>
       </c>
       <c r="E12" t="n">
         <v>11.76</v>
@@ -829,13 +851,13 @@
         <v>-17.59</v>
       </c>
       <c r="G12" t="n">
-        <v>0.8393</v>
+        <v>0.84</v>
       </c>
       <c r="H12" t="n">
-        <v>1.182</v>
+        <v>1.18</v>
       </c>
       <c r="I12" t="n">
-        <v>1.1297</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="13">
@@ -852,8 +874,10 @@
       <c r="C13" t="n">
         <v>6564.025</v>
       </c>
-      <c r="D13" t="n">
-        <v>9.6e-05</v>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>9.6e-05</t>
+        </is>
       </c>
       <c r="E13" t="n">
         <v>28.69</v>
@@ -862,13 +886,13 @@
         <v>-0.66</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5301</v>
+        <v>0.53</v>
       </c>
       <c r="H13" t="n">
-        <v>0.958</v>
+        <v>0.96</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6122</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="14">
@@ -885,8 +909,10 @@
       <c r="C14" t="n">
         <v>6562.32</v>
       </c>
-      <c r="D14" t="n">
-        <v>-7.499999999999999e-05</v>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>-7.5e-05</t>
+        </is>
       </c>
       <c r="E14" t="n">
         <v>-22.47</v>
@@ -895,13 +921,13 @@
         <v>-52.04</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2589</v>
+        <v>0.26</v>
       </c>
       <c r="H14" t="n">
-        <v>1.341</v>
+        <v>1.34</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4988</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="15">
@@ -918,8 +944,10 @@
       <c r="C15" t="n">
         <v>6563.15</v>
       </c>
-      <c r="D15" t="n">
-        <v>5.1e-05</v>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>5.1e-05</t>
+        </is>
       </c>
       <c r="E15" t="n">
         <v>15.42</v>
@@ -928,13 +956,13 @@
         <v>-14.15</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6791</v>
+        <v>0.68</v>
       </c>
       <c r="H15" t="n">
-        <v>1.078</v>
+        <v>1.08</v>
       </c>
       <c r="I15" t="n">
-        <v>0.9015</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="16">
@@ -951,8 +979,10 @@
       <c r="C16" t="n">
         <v>6564.027</v>
       </c>
-      <c r="D16" t="n">
-        <v>9.6e-05</v>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>9.6e-05</t>
+        </is>
       </c>
       <c r="E16" t="n">
         <v>28.76</v>
@@ -961,13 +991,13 @@
         <v>-0.8100000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4903</v>
+        <v>0.49</v>
       </c>
       <c r="H16" t="n">
-        <v>0.973</v>
+        <v>0.97</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6217</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="17">
@@ -984,8 +1014,10 @@
       <c r="C17" t="n">
         <v>6562.254</v>
       </c>
-      <c r="D17" t="n">
-        <v>-8.500000000000001e-05</v>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>-8.5e-05</t>
+        </is>
       </c>
       <c r="E17" t="n">
         <v>-25.49</v>
@@ -994,13 +1026,13 @@
         <v>-53.87</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2312</v>
+        <v>0.23</v>
       </c>
       <c r="H17" t="n">
-        <v>1.177</v>
+        <v>1.18</v>
       </c>
       <c r="I17" t="n">
-        <v>0.327</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="18">
@@ -1017,8 +1049,10 @@
       <c r="C18" t="n">
         <v>6563.129</v>
       </c>
-      <c r="D18" t="n">
-        <v>4.8e-05</v>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>4.8e-05</t>
+        </is>
       </c>
       <c r="E18" t="n">
         <v>14.49</v>
@@ -1027,13 +1061,13 @@
         <v>-13.89</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6444</v>
+        <v>0.64</v>
       </c>
       <c r="H18" t="n">
-        <v>1.072</v>
+        <v>1.07</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8299</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="19">
@@ -1050,8 +1084,10 @@
       <c r="C19" t="n">
         <v>6564.004</v>
       </c>
-      <c r="D19" t="n">
-        <v>9.2e-05</v>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>9.2e-05</t>
+        </is>
       </c>
       <c r="E19" t="n">
         <v>27.73</v>
@@ -1060,13 +1096,13 @@
         <v>-0.65</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5024999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="H19" t="n">
-        <v>1.003</v>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6393</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="20">
@@ -1083,8 +1119,10 @@
       <c r="C20" t="n">
         <v>6562.396</v>
       </c>
-      <c r="D20" t="n">
-        <v>-6.3e-05</v>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>-6.3e-05</t>
+        </is>
       </c>
       <c r="E20" t="n">
         <v>-18.99</v>
@@ -1093,13 +1131,13 @@
         <v>-46.48</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4129</v>
+        <v>0.41</v>
       </c>
       <c r="H20" t="n">
-        <v>1.111</v>
+        <v>1.11</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6548</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="21">
@@ -1116,8 +1154,10 @@
       <c r="C21" t="n">
         <v>6563.039</v>
       </c>
-      <c r="D21" t="n">
-        <v>3.5e-05</v>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>3.5e-05</t>
+        </is>
       </c>
       <c r="E21" t="n">
         <v>10.38</v>
@@ -1126,13 +1166,13 @@
         <v>-17.11</v>
       </c>
       <c r="G21" t="n">
-        <v>0.7056</v>
+        <v>0.71</v>
       </c>
       <c r="H21" t="n">
-        <v>1.246</v>
+        <v>1.25</v>
       </c>
       <c r="I21" t="n">
-        <v>1.062</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="22">
@@ -1149,8 +1189,10 @@
       <c r="C22" t="n">
         <v>6563.991</v>
       </c>
-      <c r="D22" t="n">
-        <v>9.1e-05</v>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>9.1e-05</t>
+        </is>
       </c>
       <c r="E22" t="n">
         <v>27.14</v>
@@ -1159,13 +1201,13 @@
         <v>-0.35</v>
       </c>
       <c r="G22" t="n">
-        <v>0.4998</v>
+        <v>0.5</v>
       </c>
       <c r="H22" t="n">
-        <v>1.041</v>
+        <v>1.04</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6685</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="23">
@@ -1182,8 +1224,10 @@
       <c r="C23" t="n">
         <v>6562.36</v>
       </c>
-      <c r="D23" t="n">
-        <v>-6.9e-05</v>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>-6.9e-05</t>
+        </is>
       </c>
       <c r="E23" t="n">
         <v>-20.65</v>
@@ -1192,13 +1236,13 @@
         <v>-46.67</v>
       </c>
       <c r="G23" t="n">
-        <v>0.3915</v>
+        <v>0.39</v>
       </c>
       <c r="H23" t="n">
         <v>1.1</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5137</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="24">
@@ -1215,8 +1259,10 @@
       <c r="C24" t="n">
         <v>6563.027</v>
       </c>
-      <c r="D24" t="n">
-        <v>3.3e-05</v>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>3.3e-05</t>
+        </is>
       </c>
       <c r="E24" t="n">
         <v>9.83</v>
@@ -1225,13 +1271,13 @@
         <v>-16.19</v>
       </c>
       <c r="G24" t="n">
-        <v>0.6941000000000001</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>1.226</v>
+        <v>1.23</v>
       </c>
       <c r="I24" t="n">
-        <v>1.0146</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="25">
@@ -1248,8 +1294,10 @@
       <c r="C25" t="n">
         <v>6563.982</v>
       </c>
-      <c r="D25" t="n">
-        <v>8.899999999999999e-05</v>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>8.9e-05</t>
+        </is>
       </c>
       <c r="E25" t="n">
         <v>26.71</v>
@@ -1258,13 +1306,13 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5061</v>
+        <v>0.51</v>
       </c>
       <c r="H25" t="n">
-        <v>1.025</v>
+        <v>1.02</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6525</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="26">
@@ -1281,8 +1329,10 @@
       <c r="C26" t="n">
         <v>6562.282</v>
       </c>
-      <c r="D26" t="n">
-        <v>-8.1e-05</v>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>-8.1e-05</t>
+        </is>
       </c>
       <c r="E26" t="n">
         <v>-24.22</v>
@@ -1291,13 +1341,13 @@
         <v>-47.33</v>
       </c>
       <c r="G26" t="n">
-        <v>0.387</v>
+        <v>0.39</v>
       </c>
       <c r="H26" t="n">
-        <v>1.261</v>
+        <v>1.26</v>
       </c>
       <c r="I26" t="n">
-        <v>0.6253</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="27">
@@ -1314,8 +1364,10 @@
       <c r="C27" t="n">
         <v>6562.989</v>
       </c>
-      <c r="D27" t="n">
-        <v>2.7e-05</v>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2.7e-05</t>
+        </is>
       </c>
       <c r="E27" t="n">
         <v>8.09</v>
@@ -1324,13 +1376,13 @@
         <v>-15.02</v>
       </c>
       <c r="G27" t="n">
-        <v>0.7983</v>
+        <v>0.8</v>
       </c>
       <c r="H27" t="n">
-        <v>1.143</v>
+        <v>1.14</v>
       </c>
       <c r="I27" t="n">
-        <v>1.1694</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="28">
@@ -1347,8 +1399,10 @@
       <c r="C28" t="n">
         <v>6563.893</v>
       </c>
-      <c r="D28" t="n">
-        <v>7.6e-05</v>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>7.6e-05</t>
+        </is>
       </c>
       <c r="E28" t="n">
         <v>22.64</v>
@@ -1357,13 +1411,13 @@
         <v>-0.47</v>
       </c>
       <c r="G28" t="n">
-        <v>0.5558</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H28" t="n">
-        <v>1.056</v>
+        <v>1.06</v>
       </c>
       <c r="I28" t="n">
-        <v>0.6843</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="29">
@@ -1380,8 +1434,10 @@
       <c r="C29" t="n">
         <v>6562.24</v>
       </c>
-      <c r="D29" t="n">
-        <v>-8.7e-05</v>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>-8.7e-05</t>
+        </is>
       </c>
       <c r="E29" t="n">
         <v>-26.12</v>
@@ -1390,13 +1446,13 @@
         <v>-47.17</v>
       </c>
       <c r="G29" t="n">
-        <v>0.392</v>
+        <v>0.39</v>
       </c>
       <c r="H29" t="n">
-        <v>1.248</v>
+        <v>1.25</v>
       </c>
       <c r="I29" t="n">
-        <v>0.629</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="30">
@@ -1413,8 +1469,10 @@
       <c r="C30" t="n">
         <v>6562.919</v>
       </c>
-      <c r="D30" t="n">
-        <v>1.6e-05</v>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>1.6e-05</t>
+        </is>
       </c>
       <c r="E30" t="n">
         <v>4.89</v>
@@ -1423,13 +1481,13 @@
         <v>-16.16</v>
       </c>
       <c r="G30" t="n">
-        <v>0.8025</v>
+        <v>0.8</v>
       </c>
       <c r="H30" t="n">
-        <v>1.157</v>
+        <v>1.16</v>
       </c>
       <c r="I30" t="n">
-        <v>1.1408</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="31">
@@ -1446,8 +1504,10 @@
       <c r="C31" t="n">
         <v>6563.84</v>
       </c>
-      <c r="D31" t="n">
-        <v>6.8e-05</v>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>6.8e-05</t>
+        </is>
       </c>
       <c r="E31" t="n">
         <v>20.25</v>
@@ -1456,13 +1516,13 @@
         <v>-0.8</v>
       </c>
       <c r="G31" t="n">
-        <v>0.555</v>
+        <v>0.55</v>
       </c>
       <c r="H31" t="n">
         <v>1.05</v>
       </c>
       <c r="I31" t="n">
-        <v>0.6783</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="32">
@@ -1479,8 +1539,10 @@
       <c r="C32" t="n">
         <v>6562.184</v>
       </c>
-      <c r="D32" t="n">
-        <v>-9.6e-05</v>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>-9.6e-05</t>
+        </is>
       </c>
       <c r="E32" t="n">
         <v>-28.69</v>
@@ -1489,13 +1551,13 @@
         <v>-49.41</v>
       </c>
       <c r="G32" t="n">
-        <v>0.345</v>
+        <v>0.34</v>
       </c>
       <c r="H32" t="n">
-        <v>1.101</v>
+        <v>1.1</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4551</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="33">
@@ -1512,8 +1574,10 @@
       <c r="C33" t="n">
         <v>6562.908</v>
       </c>
-      <c r="D33" t="n">
-        <v>1.5e-05</v>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>1.5e-05</t>
+        </is>
       </c>
       <c r="E33" t="n">
         <v>4.37</v>
@@ -1522,13 +1586,13 @@
         <v>-16.35</v>
       </c>
       <c r="G33" t="n">
-        <v>0.6516</v>
+        <v>0.65</v>
       </c>
       <c r="H33" t="n">
-        <v>1.206</v>
+        <v>1.21</v>
       </c>
       <c r="I33" t="n">
-        <v>0.9522</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="34">
@@ -1545,8 +1609,10 @@
       <c r="C34" t="n">
         <v>6563.83</v>
       </c>
-      <c r="D34" t="n">
-        <v>6.600000000000001e-05</v>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>6.6e-05</t>
+        </is>
       </c>
       <c r="E34" t="n">
         <v>19.8</v>
@@ -1555,13 +1621,13 @@
         <v>-0.92</v>
       </c>
       <c r="G34" t="n">
-        <v>0.5037</v>
+        <v>0.5</v>
       </c>
       <c r="H34" t="n">
-        <v>1.025</v>
+        <v>1.02</v>
       </c>
       <c r="I34" t="n">
-        <v>0.6525</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="35">
@@ -1578,8 +1644,10 @@
       <c r="C35" t="n">
         <v>6562.111</v>
       </c>
-      <c r="D35" t="n">
-        <v>-0.000107</v>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>-0.00011</t>
+        </is>
       </c>
       <c r="E35" t="n">
         <v>-32</v>
@@ -1588,13 +1656,13 @@
         <v>-50.43</v>
       </c>
       <c r="G35" t="n">
-        <v>0.5853</v>
+        <v>0.59</v>
       </c>
       <c r="H35" t="n">
-        <v>1.013</v>
+        <v>1.01</v>
       </c>
       <c r="I35" t="n">
-        <v>0.6923</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="36">
@@ -1611,8 +1679,10 @@
       <c r="C36" t="n">
         <v>6562.735</v>
       </c>
-      <c r="D36" t="n">
-        <v>-1.2e-05</v>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>-1.2e-05</t>
+        </is>
       </c>
       <c r="E36" t="n">
         <v>-3.51</v>
@@ -1621,13 +1691,13 @@
         <v>-21.94</v>
       </c>
       <c r="G36" t="n">
-        <v>0.657</v>
+        <v>0.66</v>
       </c>
       <c r="H36" t="n">
-        <v>1.531</v>
+        <v>1.53</v>
       </c>
       <c r="I36" t="n">
-        <v>1.1751</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="37">
@@ -1644,8 +1714,10 @@
       <c r="C37" t="n">
         <v>6563.788</v>
       </c>
-      <c r="D37" t="n">
-        <v>6e-05</v>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>6e-05</t>
+        </is>
       </c>
       <c r="E37" t="n">
         <v>17.87</v>
@@ -1654,13 +1726,13 @@
         <v>-0.5600000000000001</v>
       </c>
       <c r="G37" t="n">
-        <v>0.5172</v>
+        <v>0.52</v>
       </c>
       <c r="H37" t="n">
         <v>1.07</v>
       </c>
       <c r="I37" t="n">
-        <v>0.6977</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="38">
@@ -1677,8 +1749,10 @@
       <c r="C38" t="n">
         <v>6561.993</v>
       </c>
-      <c r="D38" t="n">
-        <v>-0.000125</v>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>-0.00012</t>
+        </is>
       </c>
       <c r="E38" t="n">
         <v>-37.43</v>
@@ -1687,13 +1761,13 @@
         <v>-60.56</v>
       </c>
       <c r="G38" t="n">
-        <v>0.2545</v>
+        <v>0.25</v>
       </c>
       <c r="H38" t="n">
-        <v>1.065</v>
+        <v>1.07</v>
       </c>
       <c r="I38" t="n">
-        <v>0.4065</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="39">
@@ -1710,8 +1784,10 @@
       <c r="C39" t="n">
         <v>6562.864</v>
       </c>
-      <c r="D39" t="n">
-        <v>8e-06</v>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>8e-06</t>
+        </is>
       </c>
       <c r="E39" t="n">
         <v>2.39</v>
@@ -1720,13 +1796,13 @@
         <v>-20.74</v>
       </c>
       <c r="G39" t="n">
-        <v>0.6723</v>
+        <v>0.67</v>
       </c>
       <c r="H39" t="n">
         <v>1.2</v>
       </c>
       <c r="I39" t="n">
-        <v>0.9969</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -1743,8 +1819,10 @@
       <c r="C40" t="n">
         <v>6563.793</v>
       </c>
-      <c r="D40" t="n">
-        <v>6e-05</v>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>6e-05</t>
+        </is>
       </c>
       <c r="E40" t="n">
         <v>18.07</v>
@@ -1753,13 +1831,13 @@
         <v>-5.06</v>
       </c>
       <c r="G40" t="n">
-        <v>0.4884</v>
+        <v>0.49</v>
       </c>
       <c r="H40" t="n">
-        <v>1.026</v>
+        <v>1.03</v>
       </c>
       <c r="I40" t="n">
-        <v>0.6538</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="41">
@@ -1776,8 +1854,10 @@
       <c r="C41" t="n">
         <v>6561.89</v>
       </c>
-      <c r="D41" t="n">
-        <v>-0.00014</v>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>-0.00014</t>
+        </is>
       </c>
       <c r="E41" t="n">
         <v>-42.1</v>
@@ -1786,13 +1866,13 @@
         <v>-66.03</v>
       </c>
       <c r="G41" t="n">
-        <v>0.2088</v>
+        <v>0.21</v>
       </c>
       <c r="H41" t="n">
         <v>0.96</v>
       </c>
       <c r="I41" t="n">
-        <v>0.2419</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="42">
@@ -1809,8 +1889,10 @@
       <c r="C42" t="n">
         <v>6562.889</v>
       </c>
-      <c r="D42" t="n">
-        <v>1.2e-05</v>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1.2e-05</t>
+        </is>
       </c>
       <c r="E42" t="n">
         <v>3.53</v>
@@ -1819,13 +1901,13 @@
         <v>-20.4</v>
       </c>
       <c r="G42" t="n">
-        <v>0.6605</v>
+        <v>0.66</v>
       </c>
       <c r="H42" t="n">
         <v>1.13</v>
       </c>
       <c r="I42" t="n">
-        <v>0.9446</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="43">
@@ -1842,8 +1924,10 @@
       <c r="C43" t="n">
         <v>6563.795</v>
       </c>
-      <c r="D43" t="n">
-        <v>6.1e-05</v>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>6.1e-05</t>
+        </is>
       </c>
       <c r="E43" t="n">
         <v>18.19</v>
@@ -1852,13 +1936,13 @@
         <v>-5.74</v>
       </c>
       <c r="G43" t="n">
-        <v>0.5004</v>
+        <v>0.5</v>
       </c>
       <c r="H43" t="n">
-        <v>1.025</v>
+        <v>1.02</v>
       </c>
       <c r="I43" t="n">
-        <v>0.6525</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="44">
@@ -1875,8 +1959,10 @@
       <c r="C44" t="n">
         <v>6561.993</v>
       </c>
-      <c r="D44" t="n">
-        <v>-0.000125</v>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>-0.00012</t>
+        </is>
       </c>
       <c r="E44" t="n">
         <v>-37.42</v>
@@ -1885,13 +1971,13 @@
         <v>-63.92</v>
       </c>
       <c r="G44" t="n">
-        <v>0.2188</v>
+        <v>0.22</v>
       </c>
       <c r="H44" t="n">
-        <v>0.924</v>
+        <v>0.92</v>
       </c>
       <c r="I44" t="n">
-        <v>0.2463</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="45">
@@ -1908,8 +1994,10 @@
       <c r="C45" t="n">
         <v>6562.95</v>
       </c>
-      <c r="D45" t="n">
-        <v>2.1e-05</v>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2.1e-05</t>
+        </is>
       </c>
       <c r="E45" t="n">
         <v>6.3</v>
@@ -1918,13 +2006,13 @@
         <v>-20.2</v>
       </c>
       <c r="G45" t="n">
-        <v>0.6398</v>
+        <v>0.64</v>
       </c>
       <c r="H45" t="n">
-        <v>1.174</v>
+        <v>1.17</v>
       </c>
       <c r="I45" t="n">
-        <v>0.9154</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="46">
@@ -1941,8 +2029,10 @@
       <c r="C46" t="n">
         <v>6563.849</v>
       </c>
-      <c r="D46" t="n">
-        <v>6.9e-05</v>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>6.9e-05</t>
+        </is>
       </c>
       <c r="E46" t="n">
         <v>20.64</v>
@@ -1951,13 +2041,13 @@
         <v>-5.86</v>
       </c>
       <c r="G46" t="n">
-        <v>0.4953</v>
+        <v>0.5</v>
       </c>
       <c r="H46" t="n">
-        <v>1.025</v>
+        <v>1.02</v>
       </c>
       <c r="I46" t="n">
-        <v>0.6525</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="47">
@@ -1974,8 +2064,10 @@
       <c r="C47" t="n">
         <v>6562.1</v>
       </c>
-      <c r="D47" t="n">
-        <v>-0.000109</v>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>-0.00011</t>
+        </is>
       </c>
       <c r="E47" t="n">
         <v>-32.54</v>
@@ -1984,13 +2076,13 @@
         <v>-60.19</v>
       </c>
       <c r="G47" t="n">
-        <v>0.3017</v>
+        <v>0.3</v>
       </c>
       <c r="H47" t="n">
-        <v>1.091</v>
+        <v>1.09</v>
       </c>
       <c r="I47" t="n">
-        <v>0.4608</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="48">
@@ -2007,8 +2099,10 @@
       <c r="C48" t="n">
         <v>6562.93</v>
       </c>
-      <c r="D48" t="n">
-        <v>1.8e-05</v>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>1.8e-05</t>
+        </is>
       </c>
       <c r="E48" t="n">
         <v>5.41</v>
@@ -2017,13 +2111,13 @@
         <v>-22.24</v>
       </c>
       <c r="G48" t="n">
-        <v>0.6808999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="H48" t="n">
-        <v>1.248</v>
+        <v>1.25</v>
       </c>
       <c r="I48" t="n">
-        <v>1.0301</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="49">
@@ -2040,8 +2134,10 @@
       <c r="C49" t="n">
         <v>6563.874</v>
       </c>
-      <c r="D49" t="n">
-        <v>7.3e-05</v>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>7.3e-05</t>
+        </is>
       </c>
       <c r="E49" t="n">
         <v>21.77</v>
@@ -2050,13 +2146,13 @@
         <v>-5.88</v>
       </c>
       <c r="G49" t="n">
-        <v>0.4979</v>
+        <v>0.5</v>
       </c>
       <c r="H49" t="n">
-        <v>1.041</v>
+        <v>1.04</v>
       </c>
       <c r="I49" t="n">
-        <v>0.6685</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="50">
@@ -2073,8 +2169,10 @@
       <c r="C50" t="n">
         <v>6562.031</v>
       </c>
-      <c r="D50" t="n">
-        <v>-0.000119</v>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>-0.00012</t>
+        </is>
       </c>
       <c r="E50" t="n">
         <v>-35.67</v>
@@ -2083,13 +2181,13 @@
         <v>-63.49</v>
       </c>
       <c r="G50" t="n">
-        <v>0.2329</v>
+        <v>0.23</v>
       </c>
       <c r="H50" t="n">
-        <v>1.038</v>
+        <v>1.04</v>
       </c>
       <c r="I50" t="n">
-        <v>0.3587</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="51">
@@ -2106,8 +2204,10 @@
       <c r="C51" t="n">
         <v>6562.96</v>
       </c>
-      <c r="D51" t="n">
-        <v>2.3e-05</v>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2.3e-05</t>
+        </is>
       </c>
       <c r="E51" t="n">
         <v>6.76</v>
@@ -2116,13 +2216,13 @@
         <v>-21.06</v>
       </c>
       <c r="G51" t="n">
-        <v>0.6544</v>
+        <v>0.65</v>
       </c>
       <c r="H51" t="n">
-        <v>1.203</v>
+        <v>1.2</v>
       </c>
       <c r="I51" t="n">
-        <v>0.9794</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="52">
@@ -2139,8 +2239,10 @@
       <c r="C52" t="n">
         <v>6563.87</v>
       </c>
-      <c r="D52" t="n">
-        <v>7.2e-05</v>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>7.2e-05</t>
+        </is>
       </c>
       <c r="E52" t="n">
         <v>21.59</v>
@@ -2149,13 +2251,13 @@
         <v>-6.23</v>
       </c>
       <c r="G52" t="n">
-        <v>0.4919</v>
+        <v>0.49</v>
       </c>
       <c r="H52" t="n">
-        <v>1.046</v>
+        <v>1.05</v>
       </c>
       <c r="I52" t="n">
-        <v>0.6741</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="53">
@@ -2172,8 +2274,10 @@
       <c r="C53" t="n">
         <v>6562.099</v>
       </c>
-      <c r="D53" t="n">
-        <v>-0.000109</v>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>-0.00011</t>
+        </is>
       </c>
       <c r="E53" t="n">
         <v>-32.59</v>
@@ -2182,13 +2286,13 @@
         <v>-62.08</v>
       </c>
       <c r="G53" t="n">
-        <v>0.2755</v>
+        <v>0.28</v>
       </c>
       <c r="H53" t="n">
-        <v>1.067</v>
+        <v>1.07</v>
       </c>
       <c r="I53" t="n">
-        <v>0.3939</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="54">
@@ -2205,8 +2309,10 @@
       <c r="C54" t="n">
         <v>6562.994</v>
       </c>
-      <c r="D54" t="n">
-        <v>2.8e-05</v>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2.8e-05</t>
+        </is>
       </c>
       <c r="E54" t="n">
         <v>8.31</v>
@@ -2215,13 +2321,13 @@
         <v>-21.18</v>
       </c>
       <c r="G54" t="n">
-        <v>0.7407</v>
+        <v>0.74</v>
       </c>
       <c r="H54" t="n">
-        <v>1.259</v>
+        <v>1.26</v>
       </c>
       <c r="I54" t="n">
-        <v>1.0243</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="55">
@@ -2238,8 +2344,10 @@
       <c r="C55" t="n">
         <v>6563.948</v>
       </c>
-      <c r="D55" t="n">
-        <v>8.4e-05</v>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>8.4e-05</t>
+        </is>
       </c>
       <c r="E55" t="n">
         <v>25.15</v>
@@ -2248,13 +2356,13 @@
         <v>-4.34</v>
       </c>
       <c r="G55" t="n">
-        <v>0.5496</v>
+        <v>0.55</v>
       </c>
       <c r="H55" t="n">
-        <v>1.068</v>
+        <v>1.07</v>
       </c>
       <c r="I55" t="n">
-        <v>0.6957</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="56">
@@ -2271,8 +2379,10 @@
       <c r="C56" t="n">
         <v>6562.114</v>
       </c>
-      <c r="D56" t="n">
-        <v>-0.000106</v>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>-0.00011</t>
+        </is>
       </c>
       <c r="E56" t="n">
         <v>-31.87</v>
@@ -2281,13 +2391,13 @@
         <v>-61.38</v>
       </c>
       <c r="G56" t="n">
-        <v>0.3095</v>
+        <v>0.31</v>
       </c>
       <c r="H56" t="n">
         <v>1.04</v>
       </c>
       <c r="I56" t="n">
-        <v>0.4263</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="57">
@@ -2304,8 +2414,10 @@
       <c r="C57" t="n">
         <v>6562.939</v>
       </c>
-      <c r="D57" t="n">
-        <v>1.9e-05</v>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>1.9e-05</t>
+        </is>
       </c>
       <c r="E57" t="n">
         <v>5.8</v>
@@ -2314,13 +2426,13 @@
         <v>-23.71</v>
       </c>
       <c r="G57" t="n">
-        <v>0.7325</v>
+        <v>0.73</v>
       </c>
       <c r="H57" t="n">
-        <v>1.324</v>
+        <v>1.32</v>
       </c>
       <c r="I57" t="n">
-        <v>1.0691</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="58">
@@ -2337,8 +2449,10 @@
       <c r="C58" t="n">
         <v>6563.924</v>
       </c>
-      <c r="D58" t="n">
-        <v>8.000000000000001e-05</v>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>8e-05</t>
+        </is>
       </c>
       <c r="E58" t="n">
         <v>24.07</v>
@@ -2347,13 +2461,13 @@
         <v>-5.44</v>
       </c>
       <c r="G58" t="n">
-        <v>0.5484</v>
+        <v>0.55</v>
       </c>
       <c r="H58" t="n">
-        <v>1.132</v>
+        <v>1.13</v>
       </c>
       <c r="I58" t="n">
-        <v>0.7595</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="59">
@@ -2370,8 +2484,10 @@
       <c r="C59" t="n">
         <v>6562.058</v>
       </c>
-      <c r="D59" t="n">
-        <v>-0.000115</v>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>-0.00011</t>
+        </is>
       </c>
       <c r="E59" t="n">
         <v>-34.42</v>
@@ -2380,13 +2496,13 @@
         <v>-63.38</v>
       </c>
       <c r="G59" t="n">
-        <v>0.2949</v>
+        <v>0.29</v>
       </c>
       <c r="H59" t="n">
-        <v>1.058</v>
+        <v>1.06</v>
       </c>
       <c r="I59" t="n">
-        <v>0.4165</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="60">
@@ -2403,8 +2519,10 @@
       <c r="C60" t="n">
         <v>6562.944</v>
       </c>
-      <c r="D60" t="n">
-        <v>2e-05</v>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2e-05</t>
+        </is>
       </c>
       <c r="E60" t="n">
         <v>6.01</v>
@@ -2413,13 +2531,13 @@
         <v>-22.95</v>
       </c>
       <c r="G60" t="n">
-        <v>0.716</v>
+        <v>0.72</v>
       </c>
       <c r="H60" t="n">
-        <v>1.297</v>
+        <v>1.3</v>
       </c>
       <c r="I60" t="n">
-        <v>1.0139</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="61">
@@ -2436,8 +2554,10 @@
       <c r="C61" t="n">
         <v>6563.914</v>
       </c>
-      <c r="D61" t="n">
-        <v>7.9e-05</v>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>7.9e-05</t>
+        </is>
       </c>
       <c r="E61" t="n">
         <v>23.63</v>
@@ -2446,13 +2566,13 @@
         <v>-5.33</v>
       </c>
       <c r="G61" t="n">
-        <v>0.5528</v>
+        <v>0.55</v>
       </c>
       <c r="H61" t="n">
-        <v>1.149</v>
+        <v>1.15</v>
       </c>
       <c r="I61" t="n">
-        <v>0.776</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="62">
@@ -2469,8 +2589,10 @@
       <c r="C62" t="n">
         <v>6562.034</v>
       </c>
-      <c r="D62" t="n">
-        <v>-0.000119</v>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>-0.00012</t>
+        </is>
       </c>
       <c r="E62" t="n">
         <v>-35.54</v>
@@ -2479,13 +2601,13 @@
         <v>-63.75</v>
       </c>
       <c r="G62" t="n">
-        <v>0.7145</v>
+        <v>0.71</v>
       </c>
       <c r="H62" t="n">
         <v>1.1</v>
       </c>
       <c r="I62" t="n">
-        <v>0.8495</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="63">
@@ -2502,8 +2624,10 @@
       <c r="C63" t="n">
         <v>6562.634</v>
       </c>
-      <c r="D63" t="n">
-        <v>-2.7e-05</v>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>-2.7e-05</t>
+        </is>
       </c>
       <c r="E63" t="n">
         <v>-8.140000000000001</v>
@@ -2512,13 +2636,13 @@
         <v>-36.35</v>
       </c>
       <c r="G63" t="n">
-        <v>0.8189</v>
+        <v>0.82</v>
       </c>
       <c r="H63" t="n">
-        <v>1.818</v>
+        <v>1.82</v>
       </c>
       <c r="I63" t="n">
-        <v>1.6089</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="64">
@@ -2535,8 +2659,10 @@
       <c r="C64" t="n">
         <v>6563.894</v>
       </c>
-      <c r="D64" t="n">
-        <v>7.6e-05</v>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>7.6e-05</t>
+        </is>
       </c>
       <c r="E64" t="n">
         <v>22.71</v>
@@ -2545,13 +2671,13 @@
         <v>-5.5</v>
       </c>
       <c r="G64" t="n">
-        <v>0.5586</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H64" t="n">
-        <v>1.121</v>
+        <v>1.12</v>
       </c>
       <c r="I64" t="n">
-        <v>0.7483</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="65">
@@ -2568,8 +2694,10 @@
       <c r="C65" t="n">
         <v>6562.032</v>
       </c>
-      <c r="D65" t="n">
-        <v>-0.000119</v>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>-0.00012</t>
+        </is>
       </c>
       <c r="E65" t="n">
         <v>-35.64</v>
@@ -2578,13 +2706,13 @@
         <v>-62.22</v>
       </c>
       <c r="G65" t="n">
-        <v>0.5748</v>
+        <v>0.57</v>
       </c>
       <c r="H65" t="n">
-        <v>1.027</v>
+        <v>1.03</v>
       </c>
       <c r="I65" t="n">
-        <v>0.7226</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="66">
@@ -2601,8 +2729,10 @@
       <c r="C66" t="n">
         <v>6562.719</v>
       </c>
-      <c r="D66" t="n">
-        <v>-1.4e-05</v>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>-1.4e-05</t>
+        </is>
       </c>
       <c r="E66" t="n">
         <v>-4.23</v>
@@ -2611,13 +2741,13 @@
         <v>-30.81</v>
       </c>
       <c r="G66" t="n">
-        <v>0.7935</v>
+        <v>0.79</v>
       </c>
       <c r="H66" t="n">
-        <v>1.612</v>
+        <v>1.61</v>
       </c>
       <c r="I66" t="n">
-        <v>1.3921</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="67">
@@ -2634,8 +2764,10 @@
       <c r="C67" t="n">
         <v>6563.856</v>
       </c>
-      <c r="D67" t="n">
-        <v>6.999999999999999e-05</v>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>7e-05</t>
+        </is>
       </c>
       <c r="E67" t="n">
         <v>20.95</v>
@@ -2644,13 +2776,13 @@
         <v>-5.63</v>
       </c>
       <c r="G67" t="n">
-        <v>0.5547</v>
+        <v>0.55</v>
       </c>
       <c r="H67" t="n">
         <v>1.14</v>
       </c>
       <c r="I67" t="n">
-        <v>0.7673</v>
+        <v>0.77</v>
       </c>
     </row>
   </sheetData>

--- a/Datos ESPARTACO/Parámetros para análisis de Antares/resultados perfiles halpha 2024, 2025 y 2026.xlsx
+++ b/Datos ESPARTACO/Parámetros para análisis de Antares/resultados perfiles halpha 2024, 2025 y 2026.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I67"/>
+  <dimension ref="A1:I73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1738,7 +1738,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Julio 24-2026</t>
+          <t>Agosto 19-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1747,33 +1747,33 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>6561.993</v>
+        <v>6562.084</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>-0.00012</t>
+          <t>-0.00011</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>-37.43</v>
+        <v>-33.26</v>
       </c>
       <c r="F38" t="n">
-        <v>-60.56</v>
+        <v>-62.06</v>
       </c>
       <c r="G38" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="H38" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="I38" t="n">
-        <v>0.41</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Julio 24-2026</t>
+          <t>Agosto 19-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1782,33 +1782,33 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>6562.864</v>
+        <v>6563.152</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>8e-06</t>
+          <t>5.2e-05</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2.39</v>
+        <v>15.52</v>
       </c>
       <c r="F39" t="n">
-        <v>-20.74</v>
+        <v>-13.28</v>
       </c>
       <c r="G39" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="H39" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Julio 24-2026</t>
+          <t>Agosto 19-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1817,21 +1817,21 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>6563.793</v>
+        <v>6563.989</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>6e-05</t>
+          <t>9e-05</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>18.07</v>
+        <v>27.05</v>
       </c>
       <c r="F40" t="n">
-        <v>-5.06</v>
+        <v>-1.75</v>
       </c>
       <c r="G40" t="n">
-        <v>0.49</v>
+        <v>0.55</v>
       </c>
       <c r="H40" t="n">
         <v>1.03</v>
@@ -1843,7 +1843,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Julio 27-2026</t>
+          <t>Julio 24-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1852,33 +1852,33 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>6561.89</v>
+        <v>6561.993</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>-0.00014</t>
+          <t>-0.00012</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>-42.1</v>
+        <v>-37.43</v>
       </c>
       <c r="F41" t="n">
-        <v>-66.03</v>
+        <v>-60.56</v>
       </c>
       <c r="G41" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="H41" t="n">
-        <v>0.96</v>
+        <v>1.07</v>
       </c>
       <c r="I41" t="n">
-        <v>0.24</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Julio 27-2026</t>
+          <t>Julio 24-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1887,33 +1887,33 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>6562.889</v>
+        <v>6562.864</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1.2e-05</t>
+          <t>8e-06</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3.53</v>
+        <v>2.39</v>
       </c>
       <c r="F42" t="n">
-        <v>-20.4</v>
+        <v>-20.74</v>
       </c>
       <c r="G42" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="H42" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="I42" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Julio 27-2026</t>
+          <t>Julio 24-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1922,24 +1922,24 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>6563.795</v>
+        <v>6563.793</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>6.1e-05</t>
+          <t>6e-05</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>18.19</v>
+        <v>18.07</v>
       </c>
       <c r="F43" t="n">
-        <v>-5.74</v>
+        <v>-5.06</v>
       </c>
       <c r="G43" t="n">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
       <c r="H43" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="I43" t="n">
         <v>0.65</v>
@@ -1948,7 +1948,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Agosto 06-2026</t>
+          <t>Julio 27-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1957,33 +1957,33 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>6561.993</v>
+        <v>6561.89</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>-0.00012</t>
+          <t>-0.00014</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>-37.42</v>
+        <v>-42.1</v>
       </c>
       <c r="F44" t="n">
-        <v>-63.92</v>
+        <v>-66.03</v>
       </c>
       <c r="G44" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="H44" t="n">
-        <v>0.92</v>
+        <v>0.96</v>
       </c>
       <c r="I44" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Agosto 06-2026</t>
+          <t>Julio 27-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1992,33 +1992,33 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>6562.95</v>
+        <v>6562.889</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2.1e-05</t>
+          <t>1.2e-05</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6.3</v>
+        <v>3.53</v>
       </c>
       <c r="F45" t="n">
-        <v>-20.2</v>
+        <v>-20.4</v>
       </c>
       <c r="G45" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="H45" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="I45" t="n">
-        <v>0.92</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Agosto 06-2026</t>
+          <t>Julio 27-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2027,18 +2027,18 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>6563.849</v>
+        <v>6563.795</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>6.9e-05</t>
+          <t>6.1e-05</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>20.64</v>
+        <v>18.19</v>
       </c>
       <c r="F46" t="n">
-        <v>-5.86</v>
+        <v>-5.74</v>
       </c>
       <c r="G46" t="n">
         <v>0.5</v>
@@ -2053,7 +2053,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Agosto 10-2026</t>
+          <t>Agosto 06-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2062,33 +2062,33 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>6562.1</v>
+        <v>6561.993</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>-0.00011</t>
+          <t>-0.00012</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>-32.54</v>
+        <v>-37.42</v>
       </c>
       <c r="F47" t="n">
-        <v>-60.19</v>
+        <v>-63.92</v>
       </c>
       <c r="G47" t="n">
-        <v>0.3</v>
+        <v>0.22</v>
       </c>
       <c r="H47" t="n">
-        <v>1.09</v>
+        <v>0.92</v>
       </c>
       <c r="I47" t="n">
-        <v>0.46</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Agosto 10-2026</t>
+          <t>Agosto 06-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2097,33 +2097,33 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>6562.93</v>
+        <v>6562.95</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1.8e-05</t>
+          <t>2.1e-05</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5.41</v>
+        <v>6.3</v>
       </c>
       <c r="F48" t="n">
-        <v>-22.24</v>
+        <v>-20.2</v>
       </c>
       <c r="G48" t="n">
-        <v>0.68</v>
+        <v>0.64</v>
       </c>
       <c r="H48" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="I48" t="n">
-        <v>1.03</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Agosto 10-2026</t>
+          <t>Agosto 06-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2132,33 +2132,33 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>6563.874</v>
+        <v>6563.849</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>7.3e-05</t>
+          <t>6.9e-05</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>21.77</v>
+        <v>20.64</v>
       </c>
       <c r="F49" t="n">
-        <v>-5.88</v>
+        <v>-5.86</v>
       </c>
       <c r="G49" t="n">
         <v>0.5</v>
       </c>
       <c r="H49" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="I49" t="n">
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Agosto 13-2026</t>
+          <t>Agosto 10-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2167,33 +2167,33 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>6562.031</v>
+        <v>6562.1</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>-0.00012</t>
+          <t>-0.00011</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>-35.67</v>
+        <v>-32.54</v>
       </c>
       <c r="F50" t="n">
-        <v>-63.49</v>
+        <v>-60.19</v>
       </c>
       <c r="G50" t="n">
-        <v>0.23</v>
+        <v>0.3</v>
       </c>
       <c r="H50" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I50" t="n">
-        <v>0.36</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Agosto 13-2026</t>
+          <t>Agosto 10-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2202,33 +2202,33 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>6562.96</v>
+        <v>6562.93</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2.3e-05</t>
+          <t>1.8e-05</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6.76</v>
+        <v>5.41</v>
       </c>
       <c r="F51" t="n">
-        <v>-21.06</v>
+        <v>-22.24</v>
       </c>
       <c r="G51" t="n">
-        <v>0.65</v>
+        <v>0.68</v>
       </c>
       <c r="H51" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="I51" t="n">
-        <v>0.98</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Agosto 13-2026</t>
+          <t>Agosto 10-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2237,24 +2237,24 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>6563.87</v>
+        <v>6563.874</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>7.2e-05</t>
+          <t>7.3e-05</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>21.59</v>
+        <v>21.77</v>
       </c>
       <c r="F52" t="n">
-        <v>-6.23</v>
+        <v>-5.88</v>
       </c>
       <c r="G52" t="n">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="H52" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="I52" t="n">
         <v>0.67</v>
@@ -2263,7 +2263,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Agosto 28-2026</t>
+          <t>Agosto 13-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2272,33 +2272,33 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>6562.099</v>
+        <v>6562.031</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>-0.00011</t>
+          <t>-0.00012</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>-32.59</v>
+        <v>-35.67</v>
       </c>
       <c r="F53" t="n">
-        <v>-62.08</v>
+        <v>-63.49</v>
       </c>
       <c r="G53" t="n">
-        <v>0.28</v>
+        <v>0.23</v>
       </c>
       <c r="H53" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="I53" t="n">
-        <v>0.39</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Agosto 28-2026</t>
+          <t>Agosto 13-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2307,33 +2307,33 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>6562.994</v>
+        <v>6562.96</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2.8e-05</t>
+          <t>2.3e-05</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>8.31</v>
+        <v>6.76</v>
       </c>
       <c r="F54" t="n">
-        <v>-21.18</v>
+        <v>-21.06</v>
       </c>
       <c r="G54" t="n">
-        <v>0.74</v>
+        <v>0.65</v>
       </c>
       <c r="H54" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="I54" t="n">
-        <v>1.02</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Agosto 28-2026</t>
+          <t>Agosto 13-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2342,33 +2342,33 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>6563.948</v>
+        <v>6563.87</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>8.4e-05</t>
+          <t>7.2e-05</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>25.15</v>
+        <v>21.59</v>
       </c>
       <c r="F55" t="n">
-        <v>-4.34</v>
+        <v>-6.23</v>
       </c>
       <c r="G55" t="n">
-        <v>0.55</v>
+        <v>0.49</v>
       </c>
       <c r="H55" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="I55" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Septiembre 07-2026</t>
+          <t>Agosto 28-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2377,7 +2377,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>6562.114</v>
+        <v>6562.099</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -2385,25 +2385,25 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>-31.87</v>
+        <v>-32.59</v>
       </c>
       <c r="F56" t="n">
-        <v>-61.38</v>
+        <v>-62.08</v>
       </c>
       <c r="G56" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="H56" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="I56" t="n">
-        <v>0.43</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Septiembre 07-2026</t>
+          <t>Agosto 28-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2412,33 +2412,33 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>6562.939</v>
+        <v>6562.994</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>1.9e-05</t>
+          <t>2.8e-05</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5.8</v>
+        <v>8.31</v>
       </c>
       <c r="F57" t="n">
-        <v>-23.71</v>
+        <v>-21.18</v>
       </c>
       <c r="G57" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="H57" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="I57" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Septiembre 07-2026</t>
+          <t>Agosto 28-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2447,33 +2447,33 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>6563.924</v>
+        <v>6563.948</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>8e-05</t>
+          <t>8.4e-05</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>24.07</v>
+        <v>25.15</v>
       </c>
       <c r="F58" t="n">
-        <v>-5.44</v>
+        <v>-4.34</v>
       </c>
       <c r="G58" t="n">
         <v>0.55</v>
       </c>
       <c r="H58" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="I58" t="n">
-        <v>0.76</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Septiembre 14-2026</t>
+          <t>Septiembre 07-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2482,7 +2482,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>6562.058</v>
+        <v>6562.114</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -2490,25 +2490,25 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>-34.42</v>
+        <v>-31.87</v>
       </c>
       <c r="F59" t="n">
-        <v>-63.38</v>
+        <v>-61.38</v>
       </c>
       <c r="G59" t="n">
-        <v>0.29</v>
+        <v>0.31</v>
       </c>
       <c r="H59" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="I59" t="n">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Septiembre 14-2026</t>
+          <t>Septiembre 07-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2517,33 +2517,33 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>6562.944</v>
+        <v>6562.939</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2e-05</t>
+          <t>1.9e-05</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6.01</v>
+        <v>5.8</v>
       </c>
       <c r="F60" t="n">
-        <v>-22.95</v>
+        <v>-23.71</v>
       </c>
       <c r="G60" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="H60" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="I60" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Septiembre 14-2026</t>
+          <t>Septiembre 07-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2552,33 +2552,33 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>6563.914</v>
+        <v>6563.924</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>7.9e-05</t>
+          <t>8e-05</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>23.63</v>
+        <v>24.07</v>
       </c>
       <c r="F61" t="n">
-        <v>-5.33</v>
+        <v>-5.44</v>
       </c>
       <c r="G61" t="n">
         <v>0.55</v>
       </c>
       <c r="H61" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="I61" t="n">
-        <v>0.78</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Septiembre 21-2026</t>
+          <t>Septiembre 14-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2587,33 +2587,33 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>6562.034</v>
+        <v>6562.058</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>-0.00012</t>
+          <t>-0.00011</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>-35.54</v>
+        <v>-34.42</v>
       </c>
       <c r="F62" t="n">
-        <v>-63.75</v>
+        <v>-63.38</v>
       </c>
       <c r="G62" t="n">
-        <v>0.71</v>
+        <v>0.29</v>
       </c>
       <c r="H62" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="I62" t="n">
-        <v>0.85</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Septiembre 21-2026</t>
+          <t>Septiembre 14-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2622,33 +2622,33 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>6562.634</v>
+        <v>6562.944</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>-2.7e-05</t>
+          <t>2e-05</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>-8.140000000000001</v>
+        <v>6.01</v>
       </c>
       <c r="F63" t="n">
-        <v>-36.35</v>
+        <v>-22.95</v>
       </c>
       <c r="G63" t="n">
-        <v>0.82</v>
+        <v>0.72</v>
       </c>
       <c r="H63" t="n">
-        <v>1.82</v>
+        <v>1.3</v>
       </c>
       <c r="I63" t="n">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Septiembre 21-2026</t>
+          <t>Septiembre 14-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2657,33 +2657,33 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>6563.894</v>
+        <v>6563.914</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>7.6e-05</t>
+          <t>7.9e-05</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>22.71</v>
+        <v>23.63</v>
       </c>
       <c r="F64" t="n">
-        <v>-5.5</v>
+        <v>-5.33</v>
       </c>
       <c r="G64" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="H64" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="I64" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Septiembre 29-2026</t>
+          <t>Septiembre 21-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2692,7 +2692,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>6562.032</v>
+        <v>6562.034</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -2700,25 +2700,25 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>-35.64</v>
+        <v>-35.54</v>
       </c>
       <c r="F65" t="n">
-        <v>-62.22</v>
+        <v>-63.75</v>
       </c>
       <c r="G65" t="n">
-        <v>0.57</v>
+        <v>0.71</v>
       </c>
       <c r="H65" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="I65" t="n">
-        <v>0.72</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Septiembre 29-2026</t>
+          <t>Septiembre 21-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2727,62 +2727,272 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>6562.719</v>
+        <v>6562.634</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>-1.4e-05</t>
+          <t>-2.7e-05</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>-4.23</v>
+        <v>-8.140000000000001</v>
       </c>
       <c r="F66" t="n">
-        <v>-30.81</v>
+        <v>-36.35</v>
       </c>
       <c r="G66" t="n">
-        <v>0.79</v>
+        <v>0.82</v>
       </c>
       <c r="H66" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="I66" t="n">
         <v>1.61</v>
-      </c>
-      <c r="I66" t="n">
-        <v>1.39</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
+          <t>Septiembre 21-2026</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Absorción Cobalto</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>6563.894</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>7.6e-05</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>22.71</v>
+      </c>
+      <c r="F67" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="H67" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
           <t>Septiembre 29-2026</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Emisión Azul Hα</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>6562.032</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>-0.00012</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>-35.64</v>
+      </c>
+      <c r="F68" t="n">
+        <v>-62.22</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H68" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Septiembre 29-2026</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Absorción Hα</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>6562.719</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>-1.4e-05</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>-4.23</v>
+      </c>
+      <c r="F69" t="n">
+        <v>-30.81</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="H69" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="I69" t="n">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Septiembre 29-2026</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
         <is>
           <t>Absorción Cobalto</t>
         </is>
       </c>
-      <c r="C67" t="n">
+      <c r="C70" t="n">
         <v>6563.856</v>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>7e-05</t>
         </is>
       </c>
-      <c r="E67" t="n">
+      <c r="E70" t="n">
         <v>20.95</v>
       </c>
-      <c r="F67" t="n">
+      <c r="F70" t="n">
         <v>-5.63</v>
       </c>
-      <c r="G67" t="n">
+      <c r="G70" t="n">
         <v>0.55</v>
       </c>
-      <c r="H67" t="n">
+      <c r="H70" t="n">
         <v>1.14</v>
       </c>
-      <c r="I67" t="n">
+      <c r="I70" t="n">
         <v>0.77</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Octubre 16-2026</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Emisión Azul Hα</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>6561.934</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>-0.00013</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>-40.1</v>
+      </c>
+      <c r="F71" t="n">
+        <v>-61.71</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="H71" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Octubre 16-2026</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Absorción Hα</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>6562.575</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>-3.6e-05</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>-10.83</v>
+      </c>
+      <c r="F72" t="n">
+        <v>-32.44</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="H72" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="I72" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Octubre 16-2026</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Absorción Cobalto</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>6563.711</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>4.8e-05</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>14.36</v>
+      </c>
+      <c r="F73" t="n">
+        <v>-7.25</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H73" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.79</v>
       </c>
     </row>
   </sheetData>
